--- a/v2025/dados/dados-originais/quadro_estatais_v4.xlsx
+++ b/v2025/dados/dados-originais/quadro_estatais_v4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\STN 2025\empresas-estados-master\v2025\dados\dados-originais\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\empresas-estados\v2025\dados\dados-originais\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CEB230-CF78-41CD-A56A-E26FC936118B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E294F62-78A8-4690-AA97-C74744AC8FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5405" uniqueCount="1353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5405" uniqueCount="1352">
   <si>
     <t>UF</t>
   </si>
@@ -2427,9 +2427,6 @@
   </si>
   <si>
     <t>24.812.554/0001-51</t>
-  </si>
-  <si>
-    <t>INFORMATICA E TECNOLOGIA DA INFORMAÇÃO</t>
   </si>
   <si>
     <t>14</t>
@@ -4648,7 +4645,7 @@
         <v>29</v>
       </c>
       <c r="AE1" s="5" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="AF1" s="5" t="s">
         <v>30</v>
@@ -4675,10 +4672,10 @@
         <v>37</v>
       </c>
       <c r="AN1" s="5" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="AO1" s="5" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="AP1" s="2"/>
     </row>
@@ -25808,7 +25805,7 @@
         <v>90</v>
       </c>
       <c r="F172" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="G172" t="s">
         <v>44</v>
@@ -25829,19 +25826,19 @@
         <v>68</v>
       </c>
       <c r="M172" t="s">
+        <v>796</v>
+      </c>
+      <c r="N172" t="s">
+        <v>47</v>
+      </c>
+      <c r="O172" t="s">
+        <v>50</v>
+      </c>
+      <c r="P172" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q172" t="s">
         <v>797</v>
-      </c>
-      <c r="N172" t="s">
-        <v>47</v>
-      </c>
-      <c r="O172" t="s">
-        <v>50</v>
-      </c>
-      <c r="P172" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q172" t="s">
-        <v>798</v>
       </c>
       <c r="R172" s="1">
         <v>3443022.26</v>
@@ -25921,19 +25918,19 @@
         <v>38</v>
       </c>
       <c r="B173" t="s">
+        <v>798</v>
+      </c>
+      <c r="C173" t="s">
         <v>799</v>
       </c>
-      <c r="C173" t="s">
+      <c r="D173" t="s">
         <v>800</v>
-      </c>
-      <c r="D173" t="s">
-        <v>801</v>
       </c>
       <c r="E173" t="s">
         <v>42</v>
       </c>
       <c r="F173" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G173" t="s">
         <v>44</v>
@@ -26046,19 +26043,19 @@
         <v>208</v>
       </c>
       <c r="B174" t="s">
+        <v>802</v>
+      </c>
+      <c r="C174" t="s">
         <v>803</v>
       </c>
-      <c r="C174" t="s">
+      <c r="D174" t="s">
         <v>804</v>
-      </c>
-      <c r="D174" t="s">
-        <v>805</v>
       </c>
       <c r="E174" t="s">
         <v>42</v>
       </c>
       <c r="F174" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G174" t="s">
         <v>61</v>
@@ -26079,19 +26076,19 @@
         <v>68</v>
       </c>
       <c r="M174" t="s">
+        <v>805</v>
+      </c>
+      <c r="N174" t="s">
+        <v>50</v>
+      </c>
+      <c r="O174" t="s">
+        <v>50</v>
+      </c>
+      <c r="P174" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q174" t="s">
         <v>806</v>
-      </c>
-      <c r="N174" t="s">
-        <v>50</v>
-      </c>
-      <c r="O174" t="s">
-        <v>50</v>
-      </c>
-      <c r="P174" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q174" t="s">
-        <v>807</v>
       </c>
       <c r="R174" s="1">
         <v>136009915</v>
@@ -26171,19 +26168,19 @@
         <v>57</v>
       </c>
       <c r="B175" t="s">
+        <v>807</v>
+      </c>
+      <c r="C175" t="s">
         <v>808</v>
       </c>
-      <c r="C175" t="s">
+      <c r="D175" t="s">
         <v>809</v>
-      </c>
-      <c r="D175" t="s">
-        <v>810</v>
       </c>
       <c r="E175" t="s">
         <v>42</v>
       </c>
       <c r="F175" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G175" t="s">
         <v>44</v>
@@ -26204,7 +26201,7 @@
         <v>68</v>
       </c>
       <c r="M175" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="N175" t="s">
         <v>50</v>
@@ -26296,19 +26293,19 @@
         <v>57</v>
       </c>
       <c r="B176" t="s">
+        <v>811</v>
+      </c>
+      <c r="C176" t="s">
         <v>812</v>
       </c>
-      <c r="C176" t="s">
+      <c r="D176" t="s">
         <v>813</v>
-      </c>
-      <c r="D176" t="s">
-        <v>814</v>
       </c>
       <c r="E176" t="s">
         <v>42</v>
       </c>
       <c r="F176" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G176" t="s">
         <v>61</v>
@@ -26329,19 +26326,19 @@
         <v>68</v>
       </c>
       <c r="M176" t="s">
+        <v>814</v>
+      </c>
+      <c r="N176" t="s">
+        <v>50</v>
+      </c>
+      <c r="O176" t="s">
+        <v>50</v>
+      </c>
+      <c r="P176" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q176" t="s">
         <v>815</v>
-      </c>
-      <c r="N176" t="s">
-        <v>50</v>
-      </c>
-      <c r="O176" t="s">
-        <v>50</v>
-      </c>
-      <c r="P176" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q176" t="s">
-        <v>816</v>
       </c>
       <c r="R176" s="1">
         <v>185116460</v>
@@ -26421,19 +26418,19 @@
         <v>64</v>
       </c>
       <c r="B177" t="s">
+        <v>816</v>
+      </c>
+      <c r="C177" t="s">
         <v>817</v>
       </c>
-      <c r="C177" t="s">
+      <c r="D177" t="s">
         <v>818</v>
-      </c>
-      <c r="D177" t="s">
-        <v>819</v>
       </c>
       <c r="E177" t="s">
         <v>42</v>
       </c>
       <c r="F177" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G177" t="s">
         <v>44</v>
@@ -26454,19 +26451,19 @@
         <v>48</v>
       </c>
       <c r="M177" t="s">
+        <v>819</v>
+      </c>
+      <c r="N177" t="s">
+        <v>50</v>
+      </c>
+      <c r="O177" t="s">
+        <v>50</v>
+      </c>
+      <c r="P177" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q177" t="s">
         <v>820</v>
-      </c>
-      <c r="N177" t="s">
-        <v>50</v>
-      </c>
-      <c r="O177" t="s">
-        <v>50</v>
-      </c>
-      <c r="P177" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q177" t="s">
-        <v>821</v>
       </c>
       <c r="R177" s="1">
         <v>336115591</v>
@@ -26543,19 +26540,19 @@
         <v>160</v>
       </c>
       <c r="B178" t="s">
+        <v>821</v>
+      </c>
+      <c r="C178" t="s">
         <v>822</v>
       </c>
-      <c r="C178" t="s">
+      <c r="D178" t="s">
         <v>823</v>
-      </c>
-      <c r="D178" t="s">
-        <v>824</v>
       </c>
       <c r="E178" t="s">
         <v>42</v>
       </c>
       <c r="F178" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G178" t="s">
         <v>61</v>
@@ -26576,19 +26573,19 @@
         <v>68</v>
       </c>
       <c r="M178" t="s">
+        <v>824</v>
+      </c>
+      <c r="N178" t="s">
+        <v>50</v>
+      </c>
+      <c r="O178" t="s">
+        <v>50</v>
+      </c>
+      <c r="P178" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q178" t="s">
         <v>825</v>
-      </c>
-      <c r="N178" t="s">
-        <v>50</v>
-      </c>
-      <c r="O178" t="s">
-        <v>50</v>
-      </c>
-      <c r="P178" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q178" t="s">
-        <v>826</v>
       </c>
       <c r="R178" s="1">
         <v>350204013.68000001</v>
@@ -26668,19 +26665,19 @@
         <v>259</v>
       </c>
       <c r="B179" t="s">
+        <v>826</v>
+      </c>
+      <c r="C179" t="s">
         <v>827</v>
       </c>
-      <c r="C179" t="s">
+      <c r="D179" t="s">
         <v>828</v>
-      </c>
-      <c r="D179" t="s">
-        <v>829</v>
       </c>
       <c r="E179" t="s">
         <v>42</v>
       </c>
       <c r="F179" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G179" t="s">
         <v>44</v>
@@ -26701,19 +26698,19 @@
         <v>48</v>
       </c>
       <c r="M179" t="s">
+        <v>829</v>
+      </c>
+      <c r="N179" t="s">
+        <v>50</v>
+      </c>
+      <c r="O179" t="s">
+        <v>50</v>
+      </c>
+      <c r="P179" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q179" t="s">
         <v>830</v>
-      </c>
-      <c r="N179" t="s">
-        <v>50</v>
-      </c>
-      <c r="O179" t="s">
-        <v>50</v>
-      </c>
-      <c r="P179" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q179" t="s">
-        <v>831</v>
       </c>
       <c r="R179" s="1">
         <v>82875490.269999996</v>
@@ -26793,19 +26790,19 @@
         <v>95</v>
       </c>
       <c r="B180" t="s">
+        <v>831</v>
+      </c>
+      <c r="C180" t="s">
         <v>832</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D180" t="s">
         <v>833</v>
-      </c>
-      <c r="D180" t="s">
-        <v>834</v>
       </c>
       <c r="E180" t="s">
         <v>42</v>
       </c>
       <c r="F180" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G180" t="s">
         <v>44</v>
@@ -26826,7 +26823,7 @@
         <v>48</v>
       </c>
       <c r="M180" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="N180" t="s">
         <v>50</v>
@@ -26918,19 +26915,19 @@
         <v>99</v>
       </c>
       <c r="B181" t="s">
+        <v>835</v>
+      </c>
+      <c r="C181" t="s">
         <v>836</v>
       </c>
-      <c r="C181" t="s">
+      <c r="D181" t="s">
         <v>837</v>
-      </c>
-      <c r="D181" t="s">
-        <v>838</v>
       </c>
       <c r="E181" t="s">
         <v>42</v>
       </c>
       <c r="F181" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G181" t="s">
         <v>61</v>
@@ -27043,19 +27040,19 @@
         <v>280</v>
       </c>
       <c r="B182" t="s">
+        <v>838</v>
+      </c>
+      <c r="C182" t="s">
         <v>839</v>
       </c>
-      <c r="C182" t="s">
+      <c r="D182" t="s">
         <v>840</v>
-      </c>
-      <c r="D182" t="s">
-        <v>841</v>
       </c>
       <c r="E182" t="s">
         <v>42</v>
       </c>
       <c r="F182" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G182" t="s">
         <v>61</v>
@@ -27076,19 +27073,19 @@
         <v>68</v>
       </c>
       <c r="M182" t="s">
+        <v>841</v>
+      </c>
+      <c r="N182" t="s">
+        <v>50</v>
+      </c>
+      <c r="O182" t="s">
+        <v>50</v>
+      </c>
+      <c r="P182" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q182" t="s">
         <v>842</v>
-      </c>
-      <c r="N182" t="s">
-        <v>50</v>
-      </c>
-      <c r="O182" t="s">
-        <v>50</v>
-      </c>
-      <c r="P182" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q182" t="s">
-        <v>843</v>
       </c>
       <c r="R182" s="1">
         <v>3060815.85</v>
@@ -27165,19 +27162,19 @@
         <v>280</v>
       </c>
       <c r="B183" t="s">
+        <v>843</v>
+      </c>
+      <c r="C183" t="s">
         <v>844</v>
       </c>
-      <c r="C183" t="s">
+      <c r="D183" t="s">
         <v>845</v>
-      </c>
-      <c r="D183" t="s">
-        <v>846</v>
       </c>
       <c r="E183" t="s">
         <v>42</v>
       </c>
       <c r="F183" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G183" t="s">
         <v>61</v>
@@ -27198,7 +27195,7 @@
         <v>68</v>
       </c>
       <c r="M183" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="N183" t="s">
         <v>50</v>
@@ -27290,19 +27287,19 @@
         <v>280</v>
       </c>
       <c r="B184" t="s">
+        <v>847</v>
+      </c>
+      <c r="C184" t="s">
         <v>848</v>
       </c>
-      <c r="C184" t="s">
+      <c r="D184" t="s">
         <v>849</v>
-      </c>
-      <c r="D184" t="s">
-        <v>850</v>
       </c>
       <c r="E184" t="s">
         <v>42</v>
       </c>
       <c r="F184" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G184" t="s">
         <v>61</v>
@@ -27415,19 +27412,19 @@
         <v>104</v>
       </c>
       <c r="B185" t="s">
+        <v>850</v>
+      </c>
+      <c r="C185" t="s">
         <v>851</v>
       </c>
-      <c r="C185" t="s">
+      <c r="D185" t="s">
         <v>852</v>
-      </c>
-      <c r="D185" t="s">
-        <v>853</v>
       </c>
       <c r="E185" t="s">
         <v>42</v>
       </c>
       <c r="F185" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G185" t="s">
         <v>61</v>
@@ -27448,19 +27445,19 @@
         <v>68</v>
       </c>
       <c r="M185" t="s">
+        <v>853</v>
+      </c>
+      <c r="N185" t="s">
+        <v>50</v>
+      </c>
+      <c r="O185" t="s">
+        <v>50</v>
+      </c>
+      <c r="P185" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q185" t="s">
         <v>854</v>
-      </c>
-      <c r="N185" t="s">
-        <v>50</v>
-      </c>
-      <c r="O185" t="s">
-        <v>50</v>
-      </c>
-      <c r="P185" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q185" t="s">
-        <v>855</v>
       </c>
       <c r="R185" s="1">
         <v>494676837</v>
@@ -27540,19 +27537,19 @@
         <v>118</v>
       </c>
       <c r="B186" t="s">
+        <v>855</v>
+      </c>
+      <c r="C186" t="s">
         <v>856</v>
       </c>
-      <c r="C186" t="s">
+      <c r="D186" t="s">
         <v>857</v>
-      </c>
-      <c r="D186" t="s">
-        <v>858</v>
       </c>
       <c r="E186" t="s">
         <v>42</v>
       </c>
       <c r="F186" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G186" t="s">
         <v>61</v>
@@ -27573,19 +27570,19 @@
         <v>48</v>
       </c>
       <c r="M186" t="s">
+        <v>858</v>
+      </c>
+      <c r="N186" t="s">
+        <v>50</v>
+      </c>
+      <c r="O186" t="s">
+        <v>50</v>
+      </c>
+      <c r="P186" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q186" t="s">
         <v>859</v>
-      </c>
-      <c r="N186" t="s">
-        <v>50</v>
-      </c>
-      <c r="O186" t="s">
-        <v>50</v>
-      </c>
-      <c r="P186" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q186" t="s">
-        <v>860</v>
       </c>
       <c r="R186" s="1">
         <v>168526</v>
@@ -27665,19 +27662,19 @@
         <v>450</v>
       </c>
       <c r="B187" t="s">
+        <v>860</v>
+      </c>
+      <c r="C187" t="s">
         <v>861</v>
       </c>
-      <c r="C187" t="s">
+      <c r="D187" t="s">
         <v>862</v>
-      </c>
-      <c r="D187" t="s">
-        <v>863</v>
       </c>
       <c r="E187" t="s">
         <v>90</v>
       </c>
       <c r="F187" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G187" t="s">
         <v>61</v>
@@ -27790,19 +27787,19 @@
         <v>123</v>
       </c>
       <c r="B188" t="s">
+        <v>863</v>
+      </c>
+      <c r="C188" t="s">
         <v>864</v>
       </c>
-      <c r="C188" t="s">
+      <c r="D188" t="s">
         <v>865</v>
-      </c>
-      <c r="D188" t="s">
-        <v>866</v>
       </c>
       <c r="E188" t="s">
         <v>42</v>
       </c>
       <c r="F188" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G188" t="s">
         <v>61</v>
@@ -27823,19 +27820,19 @@
         <v>68</v>
       </c>
       <c r="M188" t="s">
+        <v>866</v>
+      </c>
+      <c r="N188" t="s">
+        <v>50</v>
+      </c>
+      <c r="O188" t="s">
+        <v>50</v>
+      </c>
+      <c r="P188" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q188" t="s">
         <v>867</v>
-      </c>
-      <c r="N188" t="s">
-        <v>50</v>
-      </c>
-      <c r="O188" t="s">
-        <v>50</v>
-      </c>
-      <c r="P188" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q188" t="s">
-        <v>868</v>
       </c>
       <c r="R188" s="1">
         <v>439415934.27999997</v>
@@ -27915,19 +27912,19 @@
         <v>132</v>
       </c>
       <c r="B189" t="s">
+        <v>868</v>
+      </c>
+      <c r="C189" t="s">
         <v>869</v>
       </c>
-      <c r="C189" t="s">
+      <c r="D189" t="s">
         <v>870</v>
-      </c>
-      <c r="D189" t="s">
-        <v>871</v>
       </c>
       <c r="E189" t="s">
         <v>42</v>
       </c>
       <c r="F189" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G189" t="s">
         <v>44</v>
@@ -27948,7 +27945,7 @@
         <v>68</v>
       </c>
       <c r="M189" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="N189" t="s">
         <v>50</v>
@@ -28037,19 +28034,19 @@
         <v>136</v>
       </c>
       <c r="B190" t="s">
+        <v>872</v>
+      </c>
+      <c r="C190" t="s">
         <v>873</v>
       </c>
-      <c r="C190" t="s">
+      <c r="D190" t="s">
         <v>874</v>
-      </c>
-      <c r="D190" t="s">
-        <v>875</v>
       </c>
       <c r="E190" t="s">
         <v>42</v>
       </c>
       <c r="F190" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G190" t="s">
         <v>44</v>
@@ -28162,19 +28159,19 @@
         <v>525</v>
       </c>
       <c r="B191" t="s">
+        <v>875</v>
+      </c>
+      <c r="C191" t="s">
         <v>876</v>
       </c>
-      <c r="C191" t="s">
+      <c r="D191" t="s">
         <v>877</v>
-      </c>
-      <c r="D191" t="s">
-        <v>878</v>
       </c>
       <c r="E191" t="s">
         <v>42</v>
       </c>
       <c r="F191" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G191" t="s">
         <v>44</v>
@@ -28195,19 +28192,19 @@
         <v>68</v>
       </c>
       <c r="M191" t="s">
+        <v>878</v>
+      </c>
+      <c r="N191" t="s">
+        <v>50</v>
+      </c>
+      <c r="O191" t="s">
+        <v>50</v>
+      </c>
+      <c r="P191" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q191" t="s">
         <v>879</v>
-      </c>
-      <c r="N191" t="s">
-        <v>50</v>
-      </c>
-      <c r="O191" t="s">
-        <v>50</v>
-      </c>
-      <c r="P191" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q191" t="s">
-        <v>880</v>
       </c>
       <c r="R191" s="1">
         <v>2231633654.8400002</v>
@@ -28287,19 +28284,19 @@
         <v>525</v>
       </c>
       <c r="B192" t="s">
+        <v>880</v>
+      </c>
+      <c r="C192" t="s">
         <v>881</v>
       </c>
-      <c r="C192" t="s">
+      <c r="D192" t="s">
         <v>882</v>
-      </c>
-      <c r="D192" t="s">
-        <v>883</v>
       </c>
       <c r="E192" t="s">
         <v>42</v>
       </c>
       <c r="F192" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G192" t="s">
         <v>44</v>
@@ -28320,19 +28317,19 @@
         <v>48</v>
       </c>
       <c r="M192" t="s">
+        <v>883</v>
+      </c>
+      <c r="N192" t="s">
+        <v>50</v>
+      </c>
+      <c r="O192" t="s">
+        <v>50</v>
+      </c>
+      <c r="P192" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q192" t="s">
         <v>884</v>
-      </c>
-      <c r="N192" t="s">
-        <v>50</v>
-      </c>
-      <c r="O192" t="s">
-        <v>50</v>
-      </c>
-      <c r="P192" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q192" t="s">
-        <v>885</v>
       </c>
       <c r="R192" s="1">
         <v>187183804.68000001</v>
@@ -28412,19 +28409,19 @@
         <v>57</v>
       </c>
       <c r="B193" t="s">
+        <v>885</v>
+      </c>
+      <c r="C193" t="s">
         <v>886</v>
       </c>
-      <c r="C193" t="s">
+      <c r="D193" t="s">
         <v>887</v>
-      </c>
-      <c r="D193" t="s">
-        <v>888</v>
       </c>
       <c r="E193" t="s">
         <v>42</v>
       </c>
       <c r="F193" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G193" t="s">
         <v>61</v>
@@ -28445,19 +28442,19 @@
         <v>48</v>
       </c>
       <c r="M193" t="s">
+        <v>889</v>
+      </c>
+      <c r="N193" t="s">
+        <v>50</v>
+      </c>
+      <c r="O193" t="s">
+        <v>50</v>
+      </c>
+      <c r="P193" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q193" t="s">
         <v>890</v>
-      </c>
-      <c r="N193" t="s">
-        <v>50</v>
-      </c>
-      <c r="O193" t="s">
-        <v>50</v>
-      </c>
-      <c r="P193" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q193" t="s">
-        <v>891</v>
       </c>
       <c r="R193" s="1">
         <v>57231013.100000001</v>
@@ -28537,19 +28534,19 @@
         <v>86</v>
       </c>
       <c r="B194" t="s">
+        <v>891</v>
+      </c>
+      <c r="C194" t="s">
         <v>892</v>
       </c>
-      <c r="C194" t="s">
+      <c r="D194" t="s">
         <v>893</v>
-      </c>
-      <c r="D194" t="s">
-        <v>894</v>
       </c>
       <c r="E194" t="s">
         <v>42</v>
       </c>
       <c r="F194" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G194" t="s">
         <v>44</v>
@@ -28570,7 +28567,7 @@
         <v>48</v>
       </c>
       <c r="M194" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="N194" t="s">
         <v>50</v>
@@ -28659,19 +28656,19 @@
         <v>259</v>
       </c>
       <c r="B195" t="s">
+        <v>895</v>
+      </c>
+      <c r="C195" t="s">
         <v>896</v>
       </c>
-      <c r="C195" t="s">
+      <c r="D195" t="s">
         <v>897</v>
-      </c>
-      <c r="D195" t="s">
-        <v>898</v>
       </c>
       <c r="E195" t="s">
         <v>90</v>
       </c>
       <c r="F195" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G195" t="s">
         <v>61</v>
@@ -28692,7 +28689,7 @@
         <v>48</v>
       </c>
       <c r="M195" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="N195" t="s">
         <v>50</v>
@@ -28784,19 +28781,19 @@
         <v>99</v>
       </c>
       <c r="B196" t="s">
+        <v>899</v>
+      </c>
+      <c r="C196" t="s">
         <v>900</v>
       </c>
-      <c r="C196" t="s">
+      <c r="D196" t="s">
         <v>901</v>
-      </c>
-      <c r="D196" t="s">
-        <v>902</v>
       </c>
       <c r="E196" t="s">
         <v>90</v>
       </c>
       <c r="F196" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G196" t="s">
         <v>61</v>
@@ -28909,19 +28906,19 @@
         <v>450</v>
       </c>
       <c r="B197" t="s">
+        <v>902</v>
+      </c>
+      <c r="C197" t="s">
         <v>903</v>
       </c>
-      <c r="C197" t="s">
+      <c r="D197" t="s">
         <v>904</v>
-      </c>
-      <c r="D197" t="s">
-        <v>905</v>
       </c>
       <c r="E197" t="s">
         <v>42</v>
       </c>
       <c r="F197" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G197" t="s">
         <v>44</v>
@@ -28954,7 +28951,7 @@
         <v>47</v>
       </c>
       <c r="Q197" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="R197" s="1">
         <v>11722060.18</v>
@@ -29034,19 +29031,19 @@
         <v>123</v>
       </c>
       <c r="B198" t="s">
+        <v>906</v>
+      </c>
+      <c r="C198" t="s">
         <v>907</v>
       </c>
-      <c r="C198" t="s">
+      <c r="D198" t="s">
         <v>908</v>
-      </c>
-      <c r="D198" t="s">
-        <v>909</v>
       </c>
       <c r="E198" t="s">
         <v>42</v>
       </c>
       <c r="F198" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G198" t="s">
         <v>61</v>
@@ -29067,19 +29064,19 @@
         <v>68</v>
       </c>
       <c r="M198" t="s">
+        <v>909</v>
+      </c>
+      <c r="N198" t="s">
+        <v>50</v>
+      </c>
+      <c r="O198" t="s">
+        <v>50</v>
+      </c>
+      <c r="P198" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q198" t="s">
         <v>910</v>
-      </c>
-      <c r="N198" t="s">
-        <v>50</v>
-      </c>
-      <c r="O198" t="s">
-        <v>50</v>
-      </c>
-      <c r="P198" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q198" t="s">
-        <v>911</v>
       </c>
       <c r="R198" s="1">
         <v>170927213.81</v>
@@ -29159,19 +29156,19 @@
         <v>410</v>
       </c>
       <c r="B199" t="s">
+        <v>911</v>
+      </c>
+      <c r="C199" t="s">
         <v>912</v>
       </c>
-      <c r="C199" t="s">
+      <c r="D199" t="s">
         <v>913</v>
-      </c>
-      <c r="D199" t="s">
-        <v>914</v>
       </c>
       <c r="E199" t="s">
         <v>42</v>
       </c>
       <c r="F199" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G199" t="s">
         <v>61</v>
@@ -29284,19 +29281,19 @@
         <v>38</v>
       </c>
       <c r="B200" t="s">
+        <v>914</v>
+      </c>
+      <c r="C200" t="s">
         <v>915</v>
       </c>
-      <c r="C200" t="s">
+      <c r="D200" t="s">
         <v>916</v>
-      </c>
-      <c r="D200" t="s">
-        <v>917</v>
       </c>
       <c r="E200" t="s">
         <v>42</v>
       </c>
       <c r="F200" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G200" t="s">
         <v>61</v>
@@ -29409,19 +29406,19 @@
         <v>142</v>
       </c>
       <c r="B201" t="s">
+        <v>918</v>
+      </c>
+      <c r="C201" t="s">
         <v>919</v>
       </c>
-      <c r="C201" t="s">
+      <c r="D201" t="s">
         <v>920</v>
-      </c>
-      <c r="D201" t="s">
-        <v>921</v>
       </c>
       <c r="E201" t="s">
         <v>90</v>
       </c>
       <c r="F201" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G201" t="s">
         <v>61</v>
@@ -29531,19 +29528,19 @@
         <v>259</v>
       </c>
       <c r="B202" t="s">
+        <v>921</v>
+      </c>
+      <c r="C202" t="s">
         <v>922</v>
       </c>
-      <c r="C202" t="s">
+      <c r="D202" t="s">
         <v>923</v>
-      </c>
-      <c r="D202" t="s">
-        <v>924</v>
       </c>
       <c r="E202" t="s">
         <v>42</v>
       </c>
       <c r="F202" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G202" t="s">
         <v>61</v>
@@ -29564,7 +29561,7 @@
         <v>68</v>
       </c>
       <c r="M202" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="N202" t="s">
         <v>50</v>
@@ -29656,19 +29653,19 @@
         <v>525</v>
       </c>
       <c r="B203" t="s">
+        <v>925</v>
+      </c>
+      <c r="C203" t="s">
         <v>926</v>
       </c>
-      <c r="C203" t="s">
+      <c r="D203" t="s">
         <v>927</v>
-      </c>
-      <c r="D203" t="s">
-        <v>928</v>
       </c>
       <c r="E203" t="s">
         <v>42</v>
       </c>
       <c r="F203" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G203" t="s">
         <v>44</v>
@@ -29689,19 +29686,19 @@
         <v>48</v>
       </c>
       <c r="M203" t="s">
+        <v>928</v>
+      </c>
+      <c r="N203" t="s">
+        <v>50</v>
+      </c>
+      <c r="O203" t="s">
+        <v>50</v>
+      </c>
+      <c r="P203" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q203" t="s">
         <v>929</v>
-      </c>
-      <c r="N203" t="s">
-        <v>50</v>
-      </c>
-      <c r="O203" t="s">
-        <v>50</v>
-      </c>
-      <c r="P203" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q203" t="s">
-        <v>930</v>
       </c>
       <c r="R203" s="1">
         <v>653642847.29999995</v>
@@ -29781,19 +29778,19 @@
         <v>38</v>
       </c>
       <c r="B204" t="s">
+        <v>930</v>
+      </c>
+      <c r="C204" t="s">
         <v>931</v>
       </c>
-      <c r="C204" t="s">
+      <c r="D204" t="s">
         <v>932</v>
-      </c>
-      <c r="D204" t="s">
-        <v>933</v>
       </c>
       <c r="E204" t="s">
         <v>42</v>
       </c>
       <c r="F204" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G204" t="s">
         <v>44</v>
@@ -29906,19 +29903,19 @@
         <v>64</v>
       </c>
       <c r="B205" t="s">
+        <v>934</v>
+      </c>
+      <c r="C205" t="s">
         <v>935</v>
       </c>
-      <c r="C205" t="s">
+      <c r="D205" t="s">
         <v>936</v>
-      </c>
-      <c r="D205" t="s">
-        <v>937</v>
       </c>
       <c r="E205" t="s">
         <v>42</v>
       </c>
       <c r="F205" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G205" t="s">
         <v>44</v>
@@ -29939,7 +29936,7 @@
         <v>48</v>
       </c>
       <c r="M205" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="N205" t="s">
         <v>50</v>
@@ -30028,19 +30025,19 @@
         <v>70</v>
       </c>
       <c r="B206" t="s">
+        <v>938</v>
+      </c>
+      <c r="C206" t="s">
         <v>939</v>
       </c>
-      <c r="C206" t="s">
+      <c r="D206" t="s">
         <v>940</v>
-      </c>
-      <c r="D206" t="s">
-        <v>941</v>
       </c>
       <c r="E206" t="s">
         <v>42</v>
       </c>
       <c r="F206" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G206" t="s">
         <v>44</v>
@@ -30061,19 +30058,19 @@
         <v>48</v>
       </c>
       <c r="M206" t="s">
+        <v>941</v>
+      </c>
+      <c r="N206" t="s">
+        <v>50</v>
+      </c>
+      <c r="O206" t="s">
+        <v>50</v>
+      </c>
+      <c r="P206" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q206" t="s">
         <v>942</v>
-      </c>
-      <c r="N206" t="s">
-        <v>50</v>
-      </c>
-      <c r="O206" t="s">
-        <v>50</v>
-      </c>
-      <c r="P206" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q206" t="s">
-        <v>943</v>
       </c>
       <c r="R206" s="1">
         <v>55522.87</v>
@@ -30150,19 +30147,19 @@
         <v>160</v>
       </c>
       <c r="B207" t="s">
+        <v>943</v>
+      </c>
+      <c r="C207" t="s">
         <v>944</v>
       </c>
-      <c r="C207" t="s">
+      <c r="D207" t="s">
         <v>945</v>
-      </c>
-      <c r="D207" t="s">
-        <v>946</v>
       </c>
       <c r="E207" t="s">
         <v>42</v>
       </c>
       <c r="F207" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G207" t="s">
         <v>44</v>
@@ -30183,19 +30180,19 @@
         <v>48</v>
       </c>
       <c r="M207" t="s">
+        <v>946</v>
+      </c>
+      <c r="N207" t="s">
+        <v>50</v>
+      </c>
+      <c r="O207" t="s">
+        <v>50</v>
+      </c>
+      <c r="P207" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q207" t="s">
         <v>947</v>
-      </c>
-      <c r="N207" t="s">
-        <v>50</v>
-      </c>
-      <c r="O207" t="s">
-        <v>50</v>
-      </c>
-      <c r="P207" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q207" t="s">
-        <v>948</v>
       </c>
       <c r="R207" s="1">
         <v>43631716.640000001</v>
@@ -30275,19 +30272,19 @@
         <v>160</v>
       </c>
       <c r="B208" t="s">
+        <v>948</v>
+      </c>
+      <c r="C208" t="s">
         <v>949</v>
       </c>
-      <c r="C208" t="s">
+      <c r="D208" t="s">
         <v>950</v>
-      </c>
-      <c r="D208" t="s">
-        <v>951</v>
       </c>
       <c r="E208" t="s">
         <v>42</v>
       </c>
       <c r="F208" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G208" t="s">
         <v>44</v>
@@ -30308,19 +30305,19 @@
         <v>48</v>
       </c>
       <c r="M208" t="s">
+        <v>951</v>
+      </c>
+      <c r="N208" t="s">
+        <v>50</v>
+      </c>
+      <c r="O208" t="s">
+        <v>50</v>
+      </c>
+      <c r="P208" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q208" t="s">
         <v>952</v>
-      </c>
-      <c r="N208" t="s">
-        <v>50</v>
-      </c>
-      <c r="O208" t="s">
-        <v>50</v>
-      </c>
-      <c r="P208" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q208" t="s">
-        <v>953</v>
       </c>
       <c r="R208" s="1">
         <v>14166551.220000001</v>
@@ -30400,19 +30397,19 @@
         <v>259</v>
       </c>
       <c r="B209" t="s">
+        <v>953</v>
+      </c>
+      <c r="C209" t="s">
         <v>954</v>
       </c>
-      <c r="C209" t="s">
+      <c r="D209" t="s">
         <v>955</v>
-      </c>
-      <c r="D209" t="s">
-        <v>956</v>
       </c>
       <c r="E209" t="s">
         <v>42</v>
       </c>
       <c r="F209" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G209" t="s">
         <v>44</v>
@@ -30433,7 +30430,7 @@
         <v>48</v>
       </c>
       <c r="M209" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="N209" t="s">
         <v>50</v>
@@ -30525,19 +30522,19 @@
         <v>95</v>
       </c>
       <c r="B210" t="s">
+        <v>957</v>
+      </c>
+      <c r="C210" t="s">
+        <v>931</v>
+      </c>
+      <c r="D210" t="s">
         <v>958</v>
-      </c>
-      <c r="C210" t="s">
-        <v>932</v>
-      </c>
-      <c r="D210" t="s">
-        <v>959</v>
       </c>
       <c r="E210" t="s">
         <v>42</v>
       </c>
       <c r="F210" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G210" t="s">
         <v>44</v>
@@ -30558,19 +30555,19 @@
         <v>48</v>
       </c>
       <c r="M210" t="s">
+        <v>959</v>
+      </c>
+      <c r="N210" t="s">
+        <v>50</v>
+      </c>
+      <c r="O210" t="s">
+        <v>50</v>
+      </c>
+      <c r="P210" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q210" t="s">
         <v>960</v>
-      </c>
-      <c r="N210" t="s">
-        <v>50</v>
-      </c>
-      <c r="O210" t="s">
-        <v>50</v>
-      </c>
-      <c r="P210" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q210" t="s">
-        <v>961</v>
       </c>
       <c r="R210" s="1">
         <v>901202.54</v>
@@ -30650,19 +30647,19 @@
         <v>99</v>
       </c>
       <c r="B211" t="s">
+        <v>961</v>
+      </c>
+      <c r="C211" t="s">
         <v>962</v>
       </c>
-      <c r="C211" t="s">
+      <c r="D211" t="s">
         <v>963</v>
-      </c>
-      <c r="D211" t="s">
-        <v>964</v>
       </c>
       <c r="E211" t="s">
         <v>90</v>
       </c>
       <c r="F211" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G211" t="s">
         <v>44</v>
@@ -30775,19 +30772,19 @@
         <v>99</v>
       </c>
       <c r="B212" t="s">
+        <v>964</v>
+      </c>
+      <c r="C212" t="s">
+        <v>931</v>
+      </c>
+      <c r="D212" t="s">
         <v>965</v>
-      </c>
-      <c r="C212" t="s">
-        <v>932</v>
-      </c>
-      <c r="D212" t="s">
-        <v>966</v>
       </c>
       <c r="E212" t="s">
         <v>90</v>
       </c>
       <c r="F212" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G212" t="s">
         <v>44</v>
@@ -30900,19 +30897,19 @@
         <v>99</v>
       </c>
       <c r="B213" t="s">
+        <v>966</v>
+      </c>
+      <c r="C213" t="s">
+        <v>954</v>
+      </c>
+      <c r="D213" t="s">
         <v>967</v>
-      </c>
-      <c r="C213" t="s">
-        <v>955</v>
-      </c>
-      <c r="D213" t="s">
-        <v>968</v>
       </c>
       <c r="E213" t="s">
         <v>42</v>
       </c>
       <c r="F213" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G213" t="s">
         <v>44</v>
@@ -30933,19 +30930,19 @@
         <v>48</v>
       </c>
       <c r="M213" t="s">
+        <v>968</v>
+      </c>
+      <c r="N213" t="s">
+        <v>50</v>
+      </c>
+      <c r="O213" t="s">
+        <v>50</v>
+      </c>
+      <c r="P213" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q213" t="s">
         <v>969</v>
-      </c>
-      <c r="N213" t="s">
-        <v>50</v>
-      </c>
-      <c r="O213" t="s">
-        <v>50</v>
-      </c>
-      <c r="P213" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q213" t="s">
-        <v>970</v>
       </c>
       <c r="R213" s="1">
         <v>667113.42000000004</v>
@@ -31025,19 +31022,19 @@
         <v>170</v>
       </c>
       <c r="B214" t="s">
+        <v>970</v>
+      </c>
+      <c r="C214" t="s">
         <v>971</v>
       </c>
-      <c r="C214" t="s">
+      <c r="D214" t="s">
         <v>972</v>
-      </c>
-      <c r="D214" t="s">
-        <v>973</v>
       </c>
       <c r="E214" t="s">
         <v>42</v>
       </c>
       <c r="F214" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G214" t="s">
         <v>44</v>
@@ -31058,19 +31055,19 @@
         <v>48</v>
       </c>
       <c r="M214" t="s">
+        <v>973</v>
+      </c>
+      <c r="N214" t="s">
+        <v>50</v>
+      </c>
+      <c r="O214" t="s">
+        <v>50</v>
+      </c>
+      <c r="P214" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q214" t="s">
         <v>974</v>
-      </c>
-      <c r="N214" t="s">
-        <v>50</v>
-      </c>
-      <c r="O214" t="s">
-        <v>50</v>
-      </c>
-      <c r="P214" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q214" t="s">
-        <v>975</v>
       </c>
       <c r="R214" s="1">
         <v>851004</v>
@@ -31150,19 +31147,19 @@
         <v>109</v>
       </c>
       <c r="B215" t="s">
+        <v>975</v>
+      </c>
+      <c r="C215" t="s">
         <v>976</v>
       </c>
-      <c r="C215" t="s">
+      <c r="D215" t="s">
         <v>977</v>
-      </c>
-      <c r="D215" t="s">
-        <v>978</v>
       </c>
       <c r="E215" t="s">
         <v>42</v>
       </c>
       <c r="F215" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G215" t="s">
         <v>44</v>
@@ -31183,19 +31180,19 @@
         <v>48</v>
       </c>
       <c r="M215" t="s">
+        <v>978</v>
+      </c>
+      <c r="N215" t="s">
+        <v>50</v>
+      </c>
+      <c r="O215" t="s">
+        <v>50</v>
+      </c>
+      <c r="P215" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q215" t="s">
         <v>979</v>
-      </c>
-      <c r="N215" t="s">
-        <v>50</v>
-      </c>
-      <c r="O215" t="s">
-        <v>50</v>
-      </c>
-      <c r="P215" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q215" t="s">
-        <v>980</v>
       </c>
       <c r="R215" s="1">
         <v>117436.26</v>
@@ -31275,19 +31272,19 @@
         <v>109</v>
       </c>
       <c r="B216" t="s">
+        <v>980</v>
+      </c>
+      <c r="C216" t="s">
         <v>981</v>
       </c>
-      <c r="C216" t="s">
+      <c r="D216" t="s">
         <v>982</v>
-      </c>
-      <c r="D216" t="s">
-        <v>983</v>
       </c>
       <c r="E216" t="s">
         <v>42</v>
       </c>
       <c r="F216" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G216" t="s">
         <v>44</v>
@@ -31400,19 +31397,19 @@
         <v>118</v>
       </c>
       <c r="B217" t="s">
+        <v>983</v>
+      </c>
+      <c r="C217" t="s">
         <v>984</v>
       </c>
-      <c r="C217" t="s">
+      <c r="D217" t="s">
         <v>985</v>
-      </c>
-      <c r="D217" t="s">
-        <v>986</v>
       </c>
       <c r="E217" t="s">
         <v>42</v>
       </c>
       <c r="F217" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G217" t="s">
         <v>44</v>
@@ -31433,7 +31430,7 @@
         <v>48</v>
       </c>
       <c r="M217" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="N217" t="s">
         <v>50</v>
@@ -31525,19 +31522,19 @@
         <v>132</v>
       </c>
       <c r="B218" t="s">
+        <v>987</v>
+      </c>
+      <c r="C218" t="s">
         <v>988</v>
       </c>
-      <c r="C218" t="s">
+      <c r="D218" t="s">
         <v>989</v>
-      </c>
-      <c r="D218" t="s">
-        <v>990</v>
       </c>
       <c r="E218" t="s">
         <v>42</v>
       </c>
       <c r="F218" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G218" t="s">
         <v>44</v>
@@ -31558,19 +31555,19 @@
         <v>48</v>
       </c>
       <c r="M218" t="s">
+        <v>990</v>
+      </c>
+      <c r="N218" t="s">
+        <v>50</v>
+      </c>
+      <c r="O218" t="s">
+        <v>50</v>
+      </c>
+      <c r="P218" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q218" t="s">
         <v>991</v>
-      </c>
-      <c r="N218" t="s">
-        <v>50</v>
-      </c>
-      <c r="O218" t="s">
-        <v>50</v>
-      </c>
-      <c r="P218" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q218" t="s">
-        <v>992</v>
       </c>
       <c r="R218" s="1">
         <v>6634764.5300000003</v>
@@ -31647,19 +31644,19 @@
         <v>132</v>
       </c>
       <c r="B219" t="s">
+        <v>992</v>
+      </c>
+      <c r="C219" t="s">
         <v>993</v>
       </c>
-      <c r="C219" t="s">
+      <c r="D219" t="s">
         <v>994</v>
-      </c>
-      <c r="D219" t="s">
-        <v>995</v>
       </c>
       <c r="E219" t="s">
         <v>42</v>
       </c>
       <c r="F219" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G219" t="s">
         <v>44</v>
@@ -31680,19 +31677,19 @@
         <v>48</v>
       </c>
       <c r="M219" t="s">
+        <v>995</v>
+      </c>
+      <c r="N219" t="s">
+        <v>50</v>
+      </c>
+      <c r="O219" t="s">
+        <v>50</v>
+      </c>
+      <c r="P219" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q219" t="s">
         <v>996</v>
-      </c>
-      <c r="N219" t="s">
-        <v>50</v>
-      </c>
-      <c r="O219" t="s">
-        <v>50</v>
-      </c>
-      <c r="P219" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q219" t="s">
-        <v>997</v>
       </c>
       <c r="R219" s="1">
         <v>26417165</v>
@@ -31769,19 +31766,19 @@
         <v>136</v>
       </c>
       <c r="B220" t="s">
+        <v>997</v>
+      </c>
+      <c r="C220" t="s">
         <v>998</v>
       </c>
-      <c r="C220" t="s">
+      <c r="D220" t="s">
         <v>999</v>
-      </c>
-      <c r="D220" t="s">
-        <v>1000</v>
       </c>
       <c r="E220" t="s">
         <v>42</v>
       </c>
       <c r="F220" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G220" t="s">
         <v>44</v>
@@ -31802,19 +31799,19 @@
         <v>48</v>
       </c>
       <c r="M220" t="s">
+        <v>1000</v>
+      </c>
+      <c r="N220" t="s">
+        <v>50</v>
+      </c>
+      <c r="O220" t="s">
+        <v>50</v>
+      </c>
+      <c r="P220" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q220" t="s">
         <v>1001</v>
-      </c>
-      <c r="N220" t="s">
-        <v>50</v>
-      </c>
-      <c r="O220" t="s">
-        <v>50</v>
-      </c>
-      <c r="P220" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q220" t="s">
-        <v>1002</v>
       </c>
       <c r="R220" s="1">
         <v>6959001.8200000003</v>
@@ -31894,19 +31891,19 @@
         <v>64</v>
       </c>
       <c r="B221" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C221" t="s">
         <v>1003</v>
       </c>
-      <c r="C221" t="s">
+      <c r="D221" t="s">
         <v>1004</v>
-      </c>
-      <c r="D221" t="s">
-        <v>1005</v>
       </c>
       <c r="E221" t="s">
         <v>42</v>
       </c>
       <c r="F221" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G221" t="s">
         <v>61</v>
@@ -31939,7 +31936,7 @@
         <v>50</v>
       </c>
       <c r="Q221" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="R221" s="1">
         <v>291104183.95999998</v>
@@ -32019,19 +32016,19 @@
         <v>575</v>
       </c>
       <c r="B222" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C222" t="s">
         <v>1008</v>
       </c>
-      <c r="C222" t="s">
+      <c r="D222" t="s">
         <v>1009</v>
-      </c>
-      <c r="D222" t="s">
-        <v>1010</v>
       </c>
       <c r="E222" t="s">
         <v>42</v>
       </c>
       <c r="F222" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G222" t="s">
         <v>44</v>
@@ -32052,19 +32049,19 @@
         <v>68</v>
       </c>
       <c r="M222" t="s">
+        <v>1010</v>
+      </c>
+      <c r="N222" t="s">
+        <v>50</v>
+      </c>
+      <c r="O222" t="s">
+        <v>50</v>
+      </c>
+      <c r="P222" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q222" t="s">
         <v>1011</v>
-      </c>
-      <c r="N222" t="s">
-        <v>50</v>
-      </c>
-      <c r="O222" t="s">
-        <v>50</v>
-      </c>
-      <c r="P222" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q222" t="s">
-        <v>1012</v>
       </c>
       <c r="R222" s="1">
         <v>426934396.68000001</v>
@@ -32144,19 +32141,19 @@
         <v>259</v>
       </c>
       <c r="B223" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C223" t="s">
         <v>1013</v>
       </c>
-      <c r="C223" t="s">
+      <c r="D223" t="s">
         <v>1014</v>
-      </c>
-      <c r="D223" t="s">
-        <v>1015</v>
       </c>
       <c r="E223" t="s">
         <v>42</v>
       </c>
       <c r="F223" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G223" t="s">
         <v>61</v>
@@ -32269,19 +32266,19 @@
         <v>95</v>
       </c>
       <c r="B224" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C224" t="s">
         <v>1016</v>
       </c>
-      <c r="C224" t="s">
+      <c r="D224" t="s">
         <v>1017</v>
-      </c>
-      <c r="D224" t="s">
-        <v>1018</v>
       </c>
       <c r="E224" t="s">
         <v>42</v>
       </c>
       <c r="F224" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G224" t="s">
         <v>44</v>
@@ -32394,19 +32391,19 @@
         <v>99</v>
       </c>
       <c r="B225" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C225" t="s">
         <v>1019</v>
       </c>
-      <c r="C225" t="s">
+      <c r="D225" t="s">
         <v>1020</v>
-      </c>
-      <c r="D225" t="s">
-        <v>1021</v>
       </c>
       <c r="E225" t="s">
         <v>42</v>
       </c>
       <c r="F225" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G225" t="s">
         <v>61</v>
@@ -32427,7 +32424,7 @@
         <v>68</v>
       </c>
       <c r="M225" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="N225" t="s">
         <v>50</v>
@@ -32519,19 +32516,19 @@
         <v>170</v>
       </c>
       <c r="B226" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C226" t="s">
         <v>1023</v>
       </c>
-      <c r="C226" t="s">
+      <c r="D226" t="s">
         <v>1024</v>
-      </c>
-      <c r="D226" t="s">
-        <v>1025</v>
       </c>
       <c r="E226" t="s">
         <v>42</v>
       </c>
       <c r="F226" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G226" t="s">
         <v>61</v>
@@ -32552,19 +32549,19 @@
         <v>68</v>
       </c>
       <c r="M226" t="s">
+        <v>1025</v>
+      </c>
+      <c r="N226" t="s">
+        <v>50</v>
+      </c>
+      <c r="O226" t="s">
+        <v>50</v>
+      </c>
+      <c r="P226" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q226" t="s">
         <v>1026</v>
-      </c>
-      <c r="N226" t="s">
-        <v>50</v>
-      </c>
-      <c r="O226" t="s">
-        <v>50</v>
-      </c>
-      <c r="P226" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q226" t="s">
-        <v>1027</v>
       </c>
       <c r="R226" s="1">
         <v>42859983.509999998</v>
@@ -32644,19 +32641,19 @@
         <v>170</v>
       </c>
       <c r="B227" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C227" t="s">
         <v>1028</v>
       </c>
-      <c r="C227" t="s">
+      <c r="D227" t="s">
         <v>1029</v>
-      </c>
-      <c r="D227" t="s">
-        <v>1030</v>
       </c>
       <c r="E227" t="s">
         <v>42</v>
       </c>
       <c r="F227" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G227" t="s">
         <v>44</v>
@@ -32677,19 +32674,19 @@
         <v>68</v>
       </c>
       <c r="M227" t="s">
+        <v>1030</v>
+      </c>
+      <c r="N227" t="s">
+        <v>50</v>
+      </c>
+      <c r="O227" t="s">
+        <v>50</v>
+      </c>
+      <c r="P227" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q227" t="s">
         <v>1031</v>
-      </c>
-      <c r="N227" t="s">
-        <v>50</v>
-      </c>
-      <c r="O227" t="s">
-        <v>50</v>
-      </c>
-      <c r="P227" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q227" t="s">
-        <v>1032</v>
       </c>
       <c r="R227" s="1">
         <v>396624308.07999998</v>
@@ -32769,19 +32766,19 @@
         <v>280</v>
       </c>
       <c r="B228" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C228" t="s">
         <v>1033</v>
       </c>
-      <c r="C228" t="s">
+      <c r="D228" t="s">
         <v>1034</v>
-      </c>
-      <c r="D228" t="s">
-        <v>1035</v>
       </c>
       <c r="E228" t="s">
         <v>42</v>
       </c>
       <c r="F228" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G228" t="s">
         <v>61</v>
@@ -32802,7 +32799,7 @@
         <v>68</v>
       </c>
       <c r="M228" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="N228" t="s">
         <v>50</v>
@@ -32894,19 +32891,19 @@
         <v>104</v>
       </c>
       <c r="B229" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C229" t="s">
         <v>1037</v>
       </c>
-      <c r="C229" t="s">
+      <c r="D229" t="s">
         <v>1038</v>
-      </c>
-      <c r="D229" t="s">
-        <v>1039</v>
       </c>
       <c r="E229" t="s">
         <v>42</v>
       </c>
       <c r="F229" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G229" t="s">
         <v>44</v>
@@ -32927,19 +32924,19 @@
         <v>68</v>
       </c>
       <c r="M229" t="s">
+        <v>1039</v>
+      </c>
+      <c r="N229" t="s">
+        <v>50</v>
+      </c>
+      <c r="O229" t="s">
+        <v>50</v>
+      </c>
+      <c r="P229" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q229" t="s">
         <v>1040</v>
-      </c>
-      <c r="N229" t="s">
-        <v>50</v>
-      </c>
-      <c r="O229" t="s">
-        <v>50</v>
-      </c>
-      <c r="P229" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q229" t="s">
-        <v>1041</v>
       </c>
       <c r="R229" s="1">
         <v>588214707.40999997</v>
@@ -33019,19 +33016,19 @@
         <v>450</v>
       </c>
       <c r="B230" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C230" t="s">
         <v>1042</v>
       </c>
-      <c r="C230" t="s">
+      <c r="D230" t="s">
         <v>1043</v>
-      </c>
-      <c r="D230" t="s">
-        <v>1044</v>
       </c>
       <c r="E230" t="s">
         <v>42</v>
       </c>
       <c r="F230" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G230" t="s">
         <v>44</v>
@@ -33052,7 +33049,7 @@
         <v>68</v>
       </c>
       <c r="M230" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="N230" t="s">
         <v>50</v>
@@ -33144,19 +33141,19 @@
         <v>123</v>
       </c>
       <c r="B231" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C231" t="s">
         <v>1046</v>
       </c>
-      <c r="C231" t="s">
+      <c r="D231" t="s">
         <v>1047</v>
-      </c>
-      <c r="D231" t="s">
-        <v>1048</v>
       </c>
       <c r="E231" t="s">
         <v>42</v>
       </c>
       <c r="F231" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G231" t="s">
         <v>44</v>
@@ -33177,19 +33174,19 @@
         <v>68</v>
       </c>
       <c r="M231" t="s">
+        <v>1048</v>
+      </c>
+      <c r="N231" t="s">
+        <v>50</v>
+      </c>
+      <c r="O231" t="s">
+        <v>50</v>
+      </c>
+      <c r="P231" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q231" t="s">
         <v>1049</v>
-      </c>
-      <c r="N231" t="s">
-        <v>50</v>
-      </c>
-      <c r="O231" t="s">
-        <v>50</v>
-      </c>
-      <c r="P231" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q231" t="s">
-        <v>1050</v>
       </c>
       <c r="R231" s="1">
         <v>225741088</v>
@@ -33269,19 +33266,19 @@
         <v>525</v>
       </c>
       <c r="B232" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C232" t="s">
         <v>1051</v>
       </c>
-      <c r="C232" t="s">
+      <c r="D232" t="s">
         <v>1052</v>
-      </c>
-      <c r="D232" t="s">
-        <v>1053</v>
       </c>
       <c r="E232" t="s">
         <v>42</v>
       </c>
       <c r="F232" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G232" t="s">
         <v>44</v>
@@ -33314,7 +33311,7 @@
         <v>47</v>
       </c>
       <c r="Q232" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="R232" s="1">
         <v>48216016</v>
@@ -33394,19 +33391,19 @@
         <v>38</v>
       </c>
       <c r="B233" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C233" t="s">
         <v>1055</v>
       </c>
-      <c r="C233" t="s">
+      <c r="D233" t="s">
         <v>1056</v>
-      </c>
-      <c r="D233" t="s">
-        <v>1057</v>
       </c>
       <c r="E233" t="s">
         <v>42</v>
       </c>
       <c r="F233" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G233" t="s">
         <v>61</v>
@@ -33519,19 +33516,19 @@
         <v>142</v>
       </c>
       <c r="B234" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C234" t="s">
         <v>1059</v>
       </c>
-      <c r="C234" t="s">
+      <c r="D234" t="s">
         <v>1060</v>
-      </c>
-      <c r="D234" t="s">
-        <v>1061</v>
       </c>
       <c r="E234" t="s">
         <v>42</v>
       </c>
       <c r="F234" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G234" t="s">
         <v>61</v>
@@ -33552,19 +33549,19 @@
         <v>68</v>
       </c>
       <c r="M234" t="s">
+        <v>1061</v>
+      </c>
+      <c r="N234" t="s">
+        <v>50</v>
+      </c>
+      <c r="O234" t="s">
+        <v>50</v>
+      </c>
+      <c r="P234" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q234" t="s">
         <v>1062</v>
-      </c>
-      <c r="N234" t="s">
-        <v>50</v>
-      </c>
-      <c r="O234" t="s">
-        <v>50</v>
-      </c>
-      <c r="P234" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q234" t="s">
-        <v>1063</v>
       </c>
       <c r="R234" s="1">
         <v>464911233</v>
@@ -33641,19 +33638,19 @@
         <v>208</v>
       </c>
       <c r="B235" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C235" t="s">
         <v>1064</v>
       </c>
-      <c r="C235" t="s">
+      <c r="D235" t="s">
         <v>1065</v>
-      </c>
-      <c r="D235" t="s">
-        <v>1066</v>
       </c>
       <c r="E235" t="s">
         <v>42</v>
       </c>
       <c r="F235" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G235" t="s">
         <v>61</v>
@@ -33686,7 +33683,7 @@
         <v>47</v>
       </c>
       <c r="Q235" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="R235" s="1">
         <v>73990520.629999995</v>
@@ -33766,19 +33763,19 @@
         <v>427</v>
       </c>
       <c r="B236" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C236" t="s">
         <v>1068</v>
       </c>
-      <c r="C236" t="s">
+      <c r="D236" t="s">
         <v>1069</v>
-      </c>
-      <c r="D236" t="s">
-        <v>1070</v>
       </c>
       <c r="E236" t="s">
         <v>42</v>
       </c>
       <c r="F236" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G236" t="s">
         <v>61</v>
@@ -33799,7 +33796,7 @@
         <v>48</v>
       </c>
       <c r="M236" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="N236" t="s">
         <v>50</v>
@@ -33811,7 +33808,7 @@
         <v>47</v>
       </c>
       <c r="Q236" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="R236" s="1">
         <v>2764377.26</v>
@@ -33891,19 +33888,19 @@
         <v>57</v>
       </c>
       <c r="B237" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C237" t="s">
         <v>1072</v>
       </c>
-      <c r="C237" t="s">
+      <c r="D237" t="s">
         <v>1073</v>
-      </c>
-      <c r="D237" t="s">
-        <v>1074</v>
       </c>
       <c r="E237" t="s">
         <v>42</v>
       </c>
       <c r="F237" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G237" t="s">
         <v>61</v>
@@ -33924,19 +33921,19 @@
         <v>48</v>
       </c>
       <c r="M237" t="s">
+        <v>1074</v>
+      </c>
+      <c r="N237" t="s">
+        <v>50</v>
+      </c>
+      <c r="O237" t="s">
+        <v>50</v>
+      </c>
+      <c r="P237" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q237" t="s">
         <v>1075</v>
-      </c>
-      <c r="N237" t="s">
-        <v>50</v>
-      </c>
-      <c r="O237" t="s">
-        <v>50</v>
-      </c>
-      <c r="P237" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q237" t="s">
-        <v>1076</v>
       </c>
       <c r="R237" s="1">
         <v>12267646.41</v>
@@ -34016,19 +34013,19 @@
         <v>57</v>
       </c>
       <c r="B238" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C238" t="s">
         <v>1077</v>
       </c>
-      <c r="C238" t="s">
+      <c r="D238" t="s">
         <v>1078</v>
-      </c>
-      <c r="D238" t="s">
-        <v>1079</v>
       </c>
       <c r="E238" t="s">
         <v>42</v>
       </c>
       <c r="F238" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G238" t="s">
         <v>61</v>
@@ -34049,19 +34046,19 @@
         <v>68</v>
       </c>
       <c r="M238" t="s">
+        <v>1079</v>
+      </c>
+      <c r="N238" t="s">
+        <v>50</v>
+      </c>
+      <c r="O238" t="s">
+        <v>50</v>
+      </c>
+      <c r="P238" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q238" t="s">
         <v>1080</v>
-      </c>
-      <c r="N238" t="s">
-        <v>50</v>
-      </c>
-      <c r="O238" t="s">
-        <v>50</v>
-      </c>
-      <c r="P238" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q238" t="s">
-        <v>1081</v>
       </c>
       <c r="R238" s="1">
         <v>5731957321.4700003</v>
@@ -34141,19 +34138,19 @@
         <v>64</v>
       </c>
       <c r="B239" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C239" t="s">
         <v>1082</v>
       </c>
-      <c r="C239" t="s">
+      <c r="D239" t="s">
         <v>1083</v>
-      </c>
-      <c r="D239" t="s">
-        <v>1084</v>
       </c>
       <c r="E239" t="s">
         <v>42</v>
       </c>
       <c r="F239" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G239" t="s">
         <v>61</v>
@@ -34174,19 +34171,19 @@
         <v>68</v>
       </c>
       <c r="M239" t="s">
+        <v>1084</v>
+      </c>
+      <c r="N239" t="s">
+        <v>50</v>
+      </c>
+      <c r="O239" t="s">
+        <v>50</v>
+      </c>
+      <c r="P239" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q239" t="s">
         <v>1085</v>
-      </c>
-      <c r="N239" t="s">
-        <v>50</v>
-      </c>
-      <c r="O239" t="s">
-        <v>50</v>
-      </c>
-      <c r="P239" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q239" t="s">
-        <v>1086</v>
       </c>
       <c r="R239" s="1">
         <v>3137018287.46</v>
@@ -34263,19 +34260,19 @@
         <v>64</v>
       </c>
       <c r="B240" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C240" t="s">
         <v>1087</v>
       </c>
-      <c r="C240" t="s">
+      <c r="D240" t="s">
         <v>1088</v>
-      </c>
-      <c r="D240" t="s">
-        <v>1089</v>
       </c>
       <c r="E240" t="s">
         <v>42</v>
       </c>
       <c r="F240" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G240" t="s">
         <v>61</v>
@@ -34296,19 +34293,19 @@
         <v>68</v>
       </c>
       <c r="M240" t="s">
+        <v>1089</v>
+      </c>
+      <c r="N240" t="s">
+        <v>50</v>
+      </c>
+      <c r="O240" t="s">
+        <v>50</v>
+      </c>
+      <c r="P240" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q240" t="s">
         <v>1090</v>
-      </c>
-      <c r="N240" t="s">
-        <v>50</v>
-      </c>
-      <c r="O240" t="s">
-        <v>50</v>
-      </c>
-      <c r="P240" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q240" t="s">
-        <v>1091</v>
       </c>
       <c r="R240" s="1">
         <v>228237130</v>
@@ -34388,19 +34385,19 @@
         <v>70</v>
       </c>
       <c r="B241" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C241" t="s">
         <v>1092</v>
       </c>
-      <c r="C241" t="s">
+      <c r="D241" t="s">
         <v>1093</v>
-      </c>
-      <c r="D241" t="s">
-        <v>1094</v>
       </c>
       <c r="E241" t="s">
         <v>42</v>
       </c>
       <c r="F241" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G241" t="s">
         <v>61</v>
@@ -34421,19 +34418,19 @@
         <v>68</v>
       </c>
       <c r="M241" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N241" t="s">
+        <v>50</v>
+      </c>
+      <c r="O241" t="s">
+        <v>50</v>
+      </c>
+      <c r="P241" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q241" t="s">
         <v>1095</v>
-      </c>
-      <c r="N241" t="s">
-        <v>50</v>
-      </c>
-      <c r="O241" t="s">
-        <v>50</v>
-      </c>
-      <c r="P241" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q241" t="s">
-        <v>1096</v>
       </c>
       <c r="R241" s="1">
         <v>2292756128.9299998</v>
@@ -34510,19 +34507,19 @@
         <v>70</v>
       </c>
       <c r="B242" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C242" t="s">
         <v>1097</v>
       </c>
-      <c r="C242" t="s">
+      <c r="D242" t="s">
         <v>1098</v>
-      </c>
-      <c r="D242" t="s">
-        <v>1099</v>
       </c>
       <c r="E242" t="s">
         <v>90</v>
       </c>
       <c r="F242" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G242" t="s">
         <v>44</v>
@@ -34632,19 +34629,19 @@
         <v>75</v>
       </c>
       <c r="B243" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C243" t="s">
         <v>1100</v>
       </c>
-      <c r="C243" t="s">
+      <c r="D243" t="s">
         <v>1101</v>
-      </c>
-      <c r="D243" t="s">
-        <v>1102</v>
       </c>
       <c r="E243" t="s">
         <v>42</v>
       </c>
       <c r="F243" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G243" t="s">
         <v>61</v>
@@ -34665,19 +34662,19 @@
         <v>68</v>
       </c>
       <c r="M243" t="s">
+        <v>1102</v>
+      </c>
+      <c r="N243" t="s">
+        <v>50</v>
+      </c>
+      <c r="O243" t="s">
+        <v>50</v>
+      </c>
+      <c r="P243" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q243" t="s">
         <v>1103</v>
-      </c>
-      <c r="N243" t="s">
-        <v>50</v>
-      </c>
-      <c r="O243" t="s">
-        <v>50</v>
-      </c>
-      <c r="P243" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q243" t="s">
-        <v>1104</v>
       </c>
       <c r="R243" s="1">
         <v>1275944356.0999999</v>
@@ -34757,19 +34754,19 @@
         <v>80</v>
       </c>
       <c r="B244" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C244" t="s">
         <v>1105</v>
       </c>
-      <c r="C244" t="s">
+      <c r="D244" t="s">
         <v>1106</v>
-      </c>
-      <c r="D244" t="s">
-        <v>1107</v>
       </c>
       <c r="E244" t="s">
         <v>42</v>
       </c>
       <c r="F244" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G244" t="s">
         <v>61</v>
@@ -34790,19 +34787,19 @@
         <v>68</v>
       </c>
       <c r="M244" t="s">
+        <v>1107</v>
+      </c>
+      <c r="N244" t="s">
+        <v>50</v>
+      </c>
+      <c r="O244" t="s">
+        <v>50</v>
+      </c>
+      <c r="P244" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q244" t="s">
         <v>1108</v>
-      </c>
-      <c r="N244" t="s">
-        <v>50</v>
-      </c>
-      <c r="O244" t="s">
-        <v>50</v>
-      </c>
-      <c r="P244" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q244" t="s">
-        <v>1109</v>
       </c>
       <c r="R244" s="1">
         <v>3305043552</v>
@@ -34882,19 +34879,19 @@
         <v>575</v>
       </c>
       <c r="B245" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C245" t="s">
         <v>1110</v>
       </c>
-      <c r="C245" t="s">
+      <c r="D245" t="s">
         <v>1111</v>
-      </c>
-      <c r="D245" t="s">
-        <v>1112</v>
       </c>
       <c r="E245" t="s">
         <v>42</v>
       </c>
       <c r="F245" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G245" t="s">
         <v>61</v>
@@ -34915,19 +34912,19 @@
         <v>68</v>
       </c>
       <c r="M245" t="s">
+        <v>1112</v>
+      </c>
+      <c r="N245" t="s">
+        <v>50</v>
+      </c>
+      <c r="O245" t="s">
+        <v>50</v>
+      </c>
+      <c r="P245" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q245" t="s">
         <v>1113</v>
-      </c>
-      <c r="N245" t="s">
-        <v>50</v>
-      </c>
-      <c r="O245" t="s">
-        <v>50</v>
-      </c>
-      <c r="P245" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q245" t="s">
-        <v>1114</v>
       </c>
       <c r="R245" s="1">
         <v>628962559.91999996</v>
@@ -35007,19 +35004,19 @@
         <v>160</v>
       </c>
       <c r="B246" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C246" t="s">
         <v>1115</v>
       </c>
-      <c r="C246" t="s">
+      <c r="D246" t="s">
         <v>1116</v>
-      </c>
-      <c r="D246" t="s">
-        <v>1117</v>
       </c>
       <c r="E246" t="s">
         <v>42</v>
       </c>
       <c r="F246" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G246" t="s">
         <v>61</v>
@@ -35040,19 +35037,19 @@
         <v>68</v>
       </c>
       <c r="M246" t="s">
+        <v>1117</v>
+      </c>
+      <c r="N246" t="s">
+        <v>50</v>
+      </c>
+      <c r="O246" t="s">
+        <v>50</v>
+      </c>
+      <c r="P246" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q246" t="s">
         <v>1118</v>
-      </c>
-      <c r="N246" t="s">
-        <v>50</v>
-      </c>
-      <c r="O246" t="s">
-        <v>50</v>
-      </c>
-      <c r="P246" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q246" t="s">
-        <v>1119</v>
       </c>
       <c r="R246" s="1">
         <v>7786456648.1000004</v>
@@ -35132,19 +35129,19 @@
         <v>160</v>
       </c>
       <c r="B247" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C247" t="s">
         <v>1120</v>
       </c>
-      <c r="C247" t="s">
+      <c r="D247" t="s">
         <v>1121</v>
-      </c>
-      <c r="D247" t="s">
-        <v>1122</v>
       </c>
       <c r="E247" t="s">
         <v>42</v>
       </c>
       <c r="F247" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G247" t="s">
         <v>61</v>
@@ -35165,19 +35162,19 @@
         <v>68</v>
       </c>
       <c r="M247" t="s">
+        <v>1122</v>
+      </c>
+      <c r="N247" t="s">
+        <v>47</v>
+      </c>
+      <c r="O247" t="s">
+        <v>50</v>
+      </c>
+      <c r="P247" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q247" t="s">
         <v>1123</v>
-      </c>
-      <c r="N247" t="s">
-        <v>47</v>
-      </c>
-      <c r="O247" t="s">
-        <v>50</v>
-      </c>
-      <c r="P247" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q247" t="s">
-        <v>1124</v>
       </c>
       <c r="R247" s="1">
         <v>91549724.530000001</v>
@@ -35257,19 +35254,19 @@
         <v>86</v>
       </c>
       <c r="B248" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C248" t="s">
         <v>1125</v>
       </c>
-      <c r="C248" t="s">
+      <c r="D248" t="s">
         <v>1126</v>
-      </c>
-      <c r="D248" t="s">
-        <v>1127</v>
       </c>
       <c r="E248" t="s">
         <v>42</v>
       </c>
       <c r="F248" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G248" t="s">
         <v>61</v>
@@ -35290,19 +35287,19 @@
         <v>68</v>
       </c>
       <c r="M248" t="s">
+        <v>1127</v>
+      </c>
+      <c r="N248" t="s">
+        <v>50</v>
+      </c>
+      <c r="O248" t="s">
+        <v>50</v>
+      </c>
+      <c r="P248" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q248" t="s">
         <v>1128</v>
-      </c>
-      <c r="N248" t="s">
-        <v>50</v>
-      </c>
-      <c r="O248" t="s">
-        <v>50</v>
-      </c>
-      <c r="P248" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q248" t="s">
-        <v>1129</v>
       </c>
       <c r="R248" s="1">
         <v>836133064.83000004</v>
@@ -35379,19 +35376,19 @@
         <v>259</v>
       </c>
       <c r="B249" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C249" t="s">
         <v>1130</v>
       </c>
-      <c r="C249" t="s">
+      <c r="D249" t="s">
         <v>1131</v>
-      </c>
-      <c r="D249" t="s">
-        <v>1132</v>
       </c>
       <c r="E249" t="s">
         <v>90</v>
       </c>
       <c r="F249" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G249" t="s">
         <v>61</v>
@@ -35504,19 +35501,19 @@
         <v>95</v>
       </c>
       <c r="B250" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C250" t="s">
         <v>1133</v>
       </c>
-      <c r="C250" t="s">
+      <c r="D250" t="s">
         <v>1134</v>
-      </c>
-      <c r="D250" t="s">
-        <v>1135</v>
       </c>
       <c r="E250" t="s">
         <v>42</v>
       </c>
       <c r="F250" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G250" t="s">
         <v>61</v>
@@ -35537,19 +35534,19 @@
         <v>68</v>
       </c>
       <c r="M250" t="s">
+        <v>1135</v>
+      </c>
+      <c r="N250" t="s">
+        <v>50</v>
+      </c>
+      <c r="O250" t="s">
+        <v>50</v>
+      </c>
+      <c r="P250" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q250" t="s">
         <v>1136</v>
-      </c>
-      <c r="N250" t="s">
-        <v>50</v>
-      </c>
-      <c r="O250" t="s">
-        <v>50</v>
-      </c>
-      <c r="P250" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q250" t="s">
-        <v>1137</v>
       </c>
       <c r="R250" s="1">
         <v>780169317.39999998</v>
@@ -35629,19 +35626,19 @@
         <v>99</v>
       </c>
       <c r="B251" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C251" t="s">
         <v>1138</v>
       </c>
-      <c r="C251" t="s">
+      <c r="D251" t="s">
         <v>1139</v>
-      </c>
-      <c r="D251" t="s">
-        <v>1140</v>
       </c>
       <c r="E251" t="s">
         <v>42</v>
       </c>
       <c r="F251" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G251" t="s">
         <v>61</v>
@@ -35662,19 +35659,19 @@
         <v>68</v>
       </c>
       <c r="M251" t="s">
+        <v>1140</v>
+      </c>
+      <c r="N251" t="s">
+        <v>50</v>
+      </c>
+      <c r="O251" t="s">
+        <v>50</v>
+      </c>
+      <c r="P251" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q251" t="s">
         <v>1141</v>
-      </c>
-      <c r="N251" t="s">
-        <v>50</v>
-      </c>
-      <c r="O251" t="s">
-        <v>50</v>
-      </c>
-      <c r="P251" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q251" t="s">
-        <v>1142</v>
       </c>
       <c r="R251" s="1">
         <v>1515059261.3099999</v>
@@ -35754,19 +35751,19 @@
         <v>170</v>
       </c>
       <c r="B252" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C252" t="s">
         <v>1143</v>
       </c>
-      <c r="C252" t="s">
+      <c r="D252" t="s">
         <v>1144</v>
-      </c>
-      <c r="D252" t="s">
-        <v>1145</v>
       </c>
       <c r="E252" t="s">
         <v>42</v>
       </c>
       <c r="F252" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G252" t="s">
         <v>61</v>
@@ -35787,19 +35784,19 @@
         <v>68</v>
       </c>
       <c r="M252" t="s">
+        <v>1145</v>
+      </c>
+      <c r="N252" t="s">
+        <v>50</v>
+      </c>
+      <c r="O252" t="s">
+        <v>50</v>
+      </c>
+      <c r="P252" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q252" t="s">
         <v>1146</v>
-      </c>
-      <c r="N252" t="s">
-        <v>50</v>
-      </c>
-      <c r="O252" t="s">
-        <v>50</v>
-      </c>
-      <c r="P252" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q252" t="s">
-        <v>1147</v>
       </c>
       <c r="R252" s="1">
         <v>2886188098.75</v>
@@ -35879,19 +35876,19 @@
         <v>280</v>
       </c>
       <c r="B253" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C253" t="s">
         <v>1148</v>
       </c>
-      <c r="C253" t="s">
+      <c r="D253" t="s">
         <v>1149</v>
-      </c>
-      <c r="D253" t="s">
-        <v>1150</v>
       </c>
       <c r="E253" t="s">
         <v>42</v>
       </c>
       <c r="F253" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G253" t="s">
         <v>61</v>
@@ -35912,7 +35909,7 @@
         <v>68</v>
       </c>
       <c r="M253" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="N253" t="s">
         <v>50</v>
@@ -36004,19 +36001,19 @@
         <v>104</v>
       </c>
       <c r="B254" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C254" t="s">
         <v>1152</v>
       </c>
-      <c r="C254" t="s">
+      <c r="D254" t="s">
         <v>1153</v>
-      </c>
-      <c r="D254" t="s">
-        <v>1154</v>
       </c>
       <c r="E254" t="s">
         <v>42</v>
       </c>
       <c r="F254" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G254" t="s">
         <v>61</v>
@@ -36037,19 +36034,19 @@
         <v>68</v>
       </c>
       <c r="M254" t="s">
+        <v>1154</v>
+      </c>
+      <c r="N254" t="s">
+        <v>50</v>
+      </c>
+      <c r="O254" t="s">
+        <v>50</v>
+      </c>
+      <c r="P254" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q254" t="s">
         <v>1155</v>
-      </c>
-      <c r="N254" t="s">
-        <v>50</v>
-      </c>
-      <c r="O254" t="s">
-        <v>50</v>
-      </c>
-      <c r="P254" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q254" t="s">
-        <v>1156</v>
       </c>
       <c r="R254" s="1">
         <v>6848218722.2799997</v>
@@ -36129,19 +36126,19 @@
         <v>109</v>
       </c>
       <c r="B255" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C255" t="s">
         <v>1157</v>
       </c>
-      <c r="C255" t="s">
+      <c r="D255" t="s">
         <v>1158</v>
-      </c>
-      <c r="D255" t="s">
-        <v>1159</v>
       </c>
       <c r="E255" t="s">
         <v>42</v>
       </c>
       <c r="F255" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G255" t="s">
         <v>61</v>
@@ -36162,19 +36159,19 @@
         <v>68</v>
       </c>
       <c r="M255" t="s">
+        <v>1159</v>
+      </c>
+      <c r="N255" t="s">
+        <v>50</v>
+      </c>
+      <c r="O255" t="s">
+        <v>50</v>
+      </c>
+      <c r="P255" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q255" t="s">
         <v>1160</v>
-      </c>
-      <c r="N255" t="s">
-        <v>50</v>
-      </c>
-      <c r="O255" t="s">
-        <v>50</v>
-      </c>
-      <c r="P255" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q255" t="s">
-        <v>1161</v>
       </c>
       <c r="R255" s="1">
         <v>2450190000</v>
@@ -36254,19 +36251,19 @@
         <v>118</v>
       </c>
       <c r="B256" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C256" t="s">
         <v>1162</v>
       </c>
-      <c r="C256" t="s">
+      <c r="D256" t="s">
         <v>1163</v>
-      </c>
-      <c r="D256" t="s">
-        <v>1164</v>
       </c>
       <c r="E256" t="s">
         <v>42</v>
       </c>
       <c r="F256" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G256" t="s">
         <v>61</v>
@@ -36287,19 +36284,19 @@
         <v>68</v>
       </c>
       <c r="M256" t="s">
+        <v>1164</v>
+      </c>
+      <c r="N256" t="s">
+        <v>50</v>
+      </c>
+      <c r="O256" t="s">
+        <v>50</v>
+      </c>
+      <c r="P256" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q256" t="s">
         <v>1165</v>
-      </c>
-      <c r="N256" t="s">
-        <v>50</v>
-      </c>
-      <c r="O256" t="s">
-        <v>50</v>
-      </c>
-      <c r="P256" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q256" t="s">
-        <v>1166</v>
       </c>
       <c r="R256" s="1">
         <v>1169220045.1400001</v>
@@ -36379,19 +36376,19 @@
         <v>450</v>
       </c>
       <c r="B257" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C257" t="s">
         <v>1167</v>
       </c>
-      <c r="C257" t="s">
+      <c r="D257" t="s">
         <v>1168</v>
-      </c>
-      <c r="D257" t="s">
-        <v>1169</v>
       </c>
       <c r="E257" t="s">
         <v>42</v>
       </c>
       <c r="F257" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G257" t="s">
         <v>61</v>
@@ -36412,19 +36409,19 @@
         <v>68</v>
       </c>
       <c r="M257" t="s">
+        <v>1169</v>
+      </c>
+      <c r="N257" t="s">
+        <v>50</v>
+      </c>
+      <c r="O257" t="s">
+        <v>50</v>
+      </c>
+      <c r="P257" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q257" t="s">
         <v>1170</v>
-      </c>
-      <c r="N257" t="s">
-        <v>50</v>
-      </c>
-      <c r="O257" t="s">
-        <v>50</v>
-      </c>
-      <c r="P257" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q257" t="s">
-        <v>1171</v>
       </c>
       <c r="R257" s="1">
         <v>215335743.49000001</v>
@@ -36504,19 +36501,19 @@
         <v>184</v>
       </c>
       <c r="B258" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C258" t="s">
         <v>1172</v>
       </c>
-      <c r="C258" t="s">
+      <c r="D258" t="s">
         <v>1173</v>
-      </c>
-      <c r="D258" t="s">
-        <v>1174</v>
       </c>
       <c r="E258" t="s">
         <v>42</v>
       </c>
       <c r="F258" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G258" t="s">
         <v>61</v>
@@ -36537,19 +36534,19 @@
         <v>68</v>
       </c>
       <c r="M258" t="s">
+        <v>1174</v>
+      </c>
+      <c r="N258" t="s">
+        <v>50</v>
+      </c>
+      <c r="O258" t="s">
+        <v>50</v>
+      </c>
+      <c r="P258" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q258" t="s">
         <v>1175</v>
-      </c>
-      <c r="N258" t="s">
-        <v>50</v>
-      </c>
-      <c r="O258" t="s">
-        <v>50</v>
-      </c>
-      <c r="P258" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q258" t="s">
-        <v>1176</v>
       </c>
       <c r="R258" s="1">
         <v>177590323.22999999</v>
@@ -36629,19 +36626,19 @@
         <v>132</v>
       </c>
       <c r="B259" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C259" t="s">
         <v>1177</v>
       </c>
-      <c r="C259" t="s">
+      <c r="D259" t="s">
         <v>1178</v>
-      </c>
-      <c r="D259" t="s">
-        <v>1179</v>
       </c>
       <c r="E259" t="s">
         <v>42</v>
       </c>
       <c r="F259" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G259" t="s">
         <v>61</v>
@@ -36662,19 +36659,19 @@
         <v>68</v>
       </c>
       <c r="M259" t="s">
+        <v>1179</v>
+      </c>
+      <c r="N259" t="s">
+        <v>50</v>
+      </c>
+      <c r="O259" t="s">
+        <v>50</v>
+      </c>
+      <c r="P259" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q259" t="s">
         <v>1180</v>
-      </c>
-      <c r="N259" t="s">
-        <v>50</v>
-      </c>
-      <c r="O259" t="s">
-        <v>50</v>
-      </c>
-      <c r="P259" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q259" t="s">
-        <v>1181</v>
       </c>
       <c r="R259" s="1">
         <v>1950409764</v>
@@ -36751,19 +36748,19 @@
         <v>136</v>
       </c>
       <c r="B260" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C260" t="s">
         <v>1182</v>
       </c>
-      <c r="C260" t="s">
+      <c r="D260" t="s">
         <v>1183</v>
-      </c>
-      <c r="D260" t="s">
-        <v>1184</v>
       </c>
       <c r="E260" t="s">
         <v>42</v>
       </c>
       <c r="F260" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G260" t="s">
         <v>61</v>
@@ -36784,19 +36781,19 @@
         <v>68</v>
       </c>
       <c r="M260" t="s">
+        <v>1184</v>
+      </c>
+      <c r="N260" t="s">
+        <v>50</v>
+      </c>
+      <c r="O260" t="s">
+        <v>50</v>
+      </c>
+      <c r="P260" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q260" t="s">
         <v>1185</v>
-      </c>
-      <c r="N260" t="s">
-        <v>50</v>
-      </c>
-      <c r="O260" t="s">
-        <v>50</v>
-      </c>
-      <c r="P260" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q260" t="s">
-        <v>1186</v>
       </c>
       <c r="R260" s="1">
         <v>862581520</v>
@@ -36876,19 +36873,19 @@
         <v>142</v>
       </c>
       <c r="B261" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C261" t="s">
         <v>1187</v>
       </c>
-      <c r="C261" t="s">
+      <c r="D261" t="s">
         <v>1188</v>
-      </c>
-      <c r="D261" t="s">
-        <v>1189</v>
       </c>
       <c r="E261" t="s">
         <v>90</v>
       </c>
       <c r="F261" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G261" t="s">
         <v>61</v>
@@ -36998,19 +36995,19 @@
         <v>80</v>
       </c>
       <c r="B262" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C262" t="s">
         <v>1191</v>
       </c>
-      <c r="C262" t="s">
+      <c r="D262" t="s">
         <v>1192</v>
-      </c>
-      <c r="D262" t="s">
-        <v>1193</v>
       </c>
       <c r="E262" t="s">
         <v>42</v>
       </c>
       <c r="F262" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G262" t="s">
         <v>61</v>
@@ -37031,19 +37028,19 @@
         <v>48</v>
       </c>
       <c r="M262" t="s">
+        <v>1193</v>
+      </c>
+      <c r="N262" t="s">
+        <v>50</v>
+      </c>
+      <c r="O262" t="s">
+        <v>50</v>
+      </c>
+      <c r="P262" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q262" t="s">
         <v>1194</v>
-      </c>
-      <c r="N262" t="s">
-        <v>50</v>
-      </c>
-      <c r="O262" t="s">
-        <v>50</v>
-      </c>
-      <c r="P262" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q262" t="s">
-        <v>1195</v>
       </c>
       <c r="R262" s="1">
         <v>3285584.49</v>
@@ -37123,19 +37120,19 @@
         <v>575</v>
       </c>
       <c r="B263" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C263" t="s">
         <v>1196</v>
       </c>
-      <c r="C263" t="s">
+      <c r="D263" t="s">
         <v>1197</v>
-      </c>
-      <c r="D263" t="s">
-        <v>1198</v>
       </c>
       <c r="E263" t="s">
         <v>42</v>
       </c>
       <c r="F263" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G263" t="s">
         <v>44</v>
@@ -37156,19 +37153,19 @@
         <v>68</v>
       </c>
       <c r="M263" t="s">
+        <v>1198</v>
+      </c>
+      <c r="N263" t="s">
+        <v>50</v>
+      </c>
+      <c r="O263" t="s">
+        <v>50</v>
+      </c>
+      <c r="P263" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q263" t="s">
         <v>1199</v>
-      </c>
-      <c r="N263" t="s">
-        <v>50</v>
-      </c>
-      <c r="O263" t="s">
-        <v>50</v>
-      </c>
-      <c r="P263" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q263" t="s">
-        <v>1200</v>
       </c>
       <c r="R263" s="1">
         <v>2203307241.9000001</v>
@@ -37248,19 +37245,19 @@
         <v>99</v>
       </c>
       <c r="B264" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C264" t="s">
         <v>1201</v>
       </c>
-      <c r="C264" t="s">
+      <c r="D264" t="s">
         <v>1202</v>
-      </c>
-      <c r="D264" t="s">
-        <v>1203</v>
       </c>
       <c r="E264" t="s">
         <v>42</v>
       </c>
       <c r="F264" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G264" t="s">
         <v>61</v>
@@ -37373,19 +37370,19 @@
         <v>170</v>
       </c>
       <c r="B265" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C265" t="s">
         <v>1204</v>
       </c>
-      <c r="C265" t="s">
+      <c r="D265" t="s">
         <v>1205</v>
-      </c>
-      <c r="D265" t="s">
-        <v>1206</v>
       </c>
       <c r="E265" t="s">
         <v>42</v>
       </c>
       <c r="F265" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G265" t="s">
         <v>61</v>
@@ -37406,19 +37403,19 @@
         <v>68</v>
       </c>
       <c r="M265" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N265" t="s">
+        <v>50</v>
+      </c>
+      <c r="O265" t="s">
+        <v>50</v>
+      </c>
+      <c r="P265" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q265" t="s">
         <v>1207</v>
-      </c>
-      <c r="N265" t="s">
-        <v>50</v>
-      </c>
-      <c r="O265" t="s">
-        <v>50</v>
-      </c>
-      <c r="P265" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q265" t="s">
-        <v>1208</v>
       </c>
       <c r="R265" s="1">
         <v>687016112.39999998</v>
@@ -37498,19 +37495,19 @@
         <v>104</v>
       </c>
       <c r="B266" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C266" t="s">
         <v>1209</v>
       </c>
-      <c r="C266" t="s">
+      <c r="D266" t="s">
         <v>1210</v>
-      </c>
-      <c r="D266" t="s">
-        <v>1211</v>
       </c>
       <c r="E266" t="s">
         <v>42</v>
       </c>
       <c r="F266" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G266" t="s">
         <v>44</v>
@@ -37531,7 +37528,7 @@
         <v>48</v>
       </c>
       <c r="M266" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="N266" t="s">
         <v>50</v>
@@ -37623,19 +37620,19 @@
         <v>109</v>
       </c>
       <c r="B267" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C267" t="s">
         <v>1213</v>
       </c>
-      <c r="C267" t="s">
+      <c r="D267" t="s">
         <v>1214</v>
-      </c>
-      <c r="D267" t="s">
-        <v>1215</v>
       </c>
       <c r="E267" t="s">
         <v>42</v>
       </c>
       <c r="F267" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G267" t="s">
         <v>61</v>
@@ -37656,7 +37653,7 @@
         <v>48</v>
       </c>
       <c r="M267" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="N267" t="s">
         <v>50</v>
@@ -37748,19 +37745,19 @@
         <v>57</v>
       </c>
       <c r="B268" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C268" t="s">
         <v>1217</v>
       </c>
-      <c r="C268" t="s">
+      <c r="D268" t="s">
         <v>1218</v>
-      </c>
-      <c r="D268" t="s">
-        <v>1219</v>
       </c>
       <c r="E268" t="s">
         <v>42</v>
       </c>
       <c r="F268" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G268" t="s">
         <v>44</v>
@@ -37781,7 +37778,7 @@
         <v>48</v>
       </c>
       <c r="M268" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="N268" t="s">
         <v>50</v>
@@ -37873,19 +37870,19 @@
         <v>64</v>
       </c>
       <c r="B269" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C269" t="s">
         <v>1222</v>
       </c>
-      <c r="C269" t="s">
+      <c r="D269" t="s">
         <v>1223</v>
-      </c>
-      <c r="D269" t="s">
-        <v>1224</v>
       </c>
       <c r="E269" t="s">
         <v>42</v>
       </c>
       <c r="F269" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G269" t="s">
         <v>61</v>
@@ -37906,19 +37903,19 @@
         <v>68</v>
       </c>
       <c r="M269" t="s">
+        <v>1224</v>
+      </c>
+      <c r="N269" t="s">
+        <v>50</v>
+      </c>
+      <c r="O269" t="s">
+        <v>50</v>
+      </c>
+      <c r="P269" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q269" t="s">
         <v>1225</v>
-      </c>
-      <c r="N269" t="s">
-        <v>50</v>
-      </c>
-      <c r="O269" t="s">
-        <v>50</v>
-      </c>
-      <c r="P269" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q269" t="s">
-        <v>1226</v>
       </c>
       <c r="R269" s="1">
         <v>244101816.68000001</v>
@@ -37995,19 +37992,19 @@
         <v>70</v>
       </c>
       <c r="B270" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C270" t="s">
         <v>1227</v>
       </c>
-      <c r="C270" t="s">
+      <c r="D270" t="s">
         <v>1228</v>
-      </c>
-      <c r="D270" t="s">
-        <v>1229</v>
       </c>
       <c r="E270" t="s">
         <v>42</v>
       </c>
       <c r="F270" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G270" t="s">
         <v>44</v>
@@ -38028,19 +38025,19 @@
         <v>48</v>
       </c>
       <c r="M270" t="s">
+        <v>1229</v>
+      </c>
+      <c r="N270" t="s">
+        <v>50</v>
+      </c>
+      <c r="O270" t="s">
+        <v>50</v>
+      </c>
+      <c r="P270" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q270" t="s">
         <v>1230</v>
-      </c>
-      <c r="N270" t="s">
-        <v>50</v>
-      </c>
-      <c r="O270" t="s">
-        <v>50</v>
-      </c>
-      <c r="P270" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q270" t="s">
-        <v>1231</v>
       </c>
       <c r="R270" s="1">
         <v>192510639.05000001</v>
@@ -38117,19 +38114,19 @@
         <v>70</v>
       </c>
       <c r="B271" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C271" t="s">
         <v>1232</v>
       </c>
-      <c r="C271" t="s">
+      <c r="D271" t="s">
         <v>1233</v>
-      </c>
-      <c r="D271" t="s">
-        <v>1234</v>
       </c>
       <c r="E271" t="s">
         <v>42</v>
       </c>
       <c r="F271" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G271" t="s">
         <v>44</v>
@@ -38150,7 +38147,7 @@
         <v>48</v>
       </c>
       <c r="M271" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="N271" t="s">
         <v>50</v>
@@ -38239,19 +38236,19 @@
         <v>75</v>
       </c>
       <c r="B272" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C272" t="s">
         <v>1236</v>
       </c>
-      <c r="C272" t="s">
+      <c r="D272" t="s">
         <v>1237</v>
-      </c>
-      <c r="D272" t="s">
-        <v>1238</v>
       </c>
       <c r="E272" t="s">
         <v>42</v>
       </c>
       <c r="F272" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G272" t="s">
         <v>44</v>
@@ -38272,7 +38269,7 @@
         <v>68</v>
       </c>
       <c r="M272" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="N272" t="s">
         <v>50</v>
@@ -38284,7 +38281,7 @@
         <v>47</v>
       </c>
       <c r="Q272" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="R272" s="1">
         <v>85695694.439999998</v>
@@ -38364,19 +38361,19 @@
         <v>80</v>
       </c>
       <c r="B273" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C273" t="s">
         <v>1240</v>
       </c>
-      <c r="C273" t="s">
+      <c r="D273" t="s">
         <v>1241</v>
-      </c>
-      <c r="D273" t="s">
-        <v>1242</v>
       </c>
       <c r="E273" t="s">
         <v>42</v>
       </c>
       <c r="F273" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G273" t="s">
         <v>61</v>
@@ -38397,19 +38394,19 @@
         <v>48</v>
       </c>
       <c r="M273" t="s">
+        <v>1242</v>
+      </c>
+      <c r="N273" t="s">
+        <v>50</v>
+      </c>
+      <c r="O273" t="s">
+        <v>50</v>
+      </c>
+      <c r="P273" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q273" t="s">
         <v>1243</v>
-      </c>
-      <c r="N273" t="s">
-        <v>50</v>
-      </c>
-      <c r="O273" t="s">
-        <v>50</v>
-      </c>
-      <c r="P273" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q273" t="s">
-        <v>1244</v>
       </c>
       <c r="R273" s="1">
         <v>137440387.50999999</v>
@@ -38489,19 +38486,19 @@
         <v>80</v>
       </c>
       <c r="B274" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C274" t="s">
         <v>1245</v>
       </c>
-      <c r="C274" t="s">
+      <c r="D274" t="s">
         <v>1246</v>
-      </c>
-      <c r="D274" t="s">
-        <v>1247</v>
       </c>
       <c r="E274" t="s">
         <v>42</v>
       </c>
       <c r="F274" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G274" t="s">
         <v>44</v>
@@ -38522,19 +38519,19 @@
         <v>68</v>
       </c>
       <c r="M274" t="s">
+        <v>1247</v>
+      </c>
+      <c r="N274" t="s">
+        <v>50</v>
+      </c>
+      <c r="O274" t="s">
+        <v>50</v>
+      </c>
+      <c r="P274" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q274" t="s">
         <v>1248</v>
-      </c>
-      <c r="N274" t="s">
-        <v>50</v>
-      </c>
-      <c r="O274" t="s">
-        <v>50</v>
-      </c>
-      <c r="P274" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q274" t="s">
-        <v>1249</v>
       </c>
       <c r="R274" s="1">
         <v>10685127.470000001</v>
@@ -38614,19 +38611,19 @@
         <v>160</v>
       </c>
       <c r="B275" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C275" t="s">
         <v>1250</v>
       </c>
-      <c r="C275" t="s">
+      <c r="D275" t="s">
         <v>1251</v>
-      </c>
-      <c r="D275" t="s">
-        <v>1252</v>
       </c>
       <c r="E275" t="s">
         <v>42</v>
       </c>
       <c r="F275" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G275" t="s">
         <v>44</v>
@@ -38659,7 +38656,7 @@
         <v>47</v>
       </c>
       <c r="Q275" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="R275" s="1">
         <v>-1569</v>
@@ -38739,19 +38736,19 @@
         <v>170</v>
       </c>
       <c r="B276" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C276" t="s">
         <v>1254</v>
       </c>
-      <c r="C276" t="s">
+      <c r="D276" t="s">
         <v>1255</v>
-      </c>
-      <c r="D276" t="s">
-        <v>1256</v>
       </c>
       <c r="E276" t="s">
         <v>42</v>
       </c>
       <c r="F276" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G276" t="s">
         <v>44</v>
@@ -38772,19 +38769,19 @@
         <v>48</v>
       </c>
       <c r="M276" t="s">
+        <v>1256</v>
+      </c>
+      <c r="N276" t="s">
+        <v>50</v>
+      </c>
+      <c r="O276" t="s">
+        <v>50</v>
+      </c>
+      <c r="P276" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q276" t="s">
         <v>1257</v>
-      </c>
-      <c r="N276" t="s">
-        <v>50</v>
-      </c>
-      <c r="O276" t="s">
-        <v>50</v>
-      </c>
-      <c r="P276" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q276" t="s">
-        <v>1258</v>
       </c>
       <c r="R276" s="1">
         <v>3713806.31</v>
@@ -38864,19 +38861,19 @@
         <v>170</v>
       </c>
       <c r="B277" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C277" t="s">
         <v>1259</v>
       </c>
-      <c r="C277" t="s">
+      <c r="D277" t="s">
         <v>1260</v>
-      </c>
-      <c r="D277" t="s">
-        <v>1261</v>
       </c>
       <c r="E277" t="s">
         <v>42</v>
       </c>
       <c r="F277" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G277" t="s">
         <v>44</v>
@@ -38897,19 +38894,19 @@
         <v>48</v>
       </c>
       <c r="M277" t="s">
+        <v>1261</v>
+      </c>
+      <c r="N277" t="s">
+        <v>50</v>
+      </c>
+      <c r="O277" t="s">
+        <v>50</v>
+      </c>
+      <c r="P277" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q277" t="s">
         <v>1262</v>
-      </c>
-      <c r="N277" t="s">
-        <v>50</v>
-      </c>
-      <c r="O277" t="s">
-        <v>50</v>
-      </c>
-      <c r="P277" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q277" t="s">
-        <v>1263</v>
       </c>
       <c r="R277" s="1">
         <v>2406453</v>
@@ -38989,19 +38986,19 @@
         <v>280</v>
       </c>
       <c r="B278" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C278" t="s">
         <v>1264</v>
       </c>
-      <c r="C278" t="s">
+      <c r="D278" t="s">
         <v>1265</v>
-      </c>
-      <c r="D278" t="s">
-        <v>1266</v>
       </c>
       <c r="E278" t="s">
         <v>42</v>
       </c>
       <c r="F278" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G278" t="s">
         <v>61</v>
@@ -39022,7 +39019,7 @@
         <v>48</v>
       </c>
       <c r="M278" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="N278" t="s">
         <v>50</v>
@@ -39114,19 +39111,19 @@
         <v>104</v>
       </c>
       <c r="B279" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C279" t="s">
         <v>1268</v>
       </c>
-      <c r="C279" t="s">
+      <c r="D279" t="s">
         <v>1269</v>
-      </c>
-      <c r="D279" t="s">
-        <v>1270</v>
       </c>
       <c r="E279" t="s">
         <v>42</v>
       </c>
       <c r="F279" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G279" t="s">
         <v>61</v>
@@ -39239,19 +39236,19 @@
         <v>109</v>
       </c>
       <c r="B280" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C280" t="s">
         <v>1271</v>
       </c>
-      <c r="C280" t="s">
+      <c r="D280" t="s">
         <v>1272</v>
-      </c>
-      <c r="D280" t="s">
-        <v>1273</v>
       </c>
       <c r="E280" t="s">
         <v>90</v>
       </c>
       <c r="F280" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G280" t="s">
         <v>44</v>
@@ -39364,19 +39361,19 @@
         <v>109</v>
       </c>
       <c r="B281" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C281" t="s">
         <v>1274</v>
       </c>
-      <c r="C281" t="s">
+      <c r="D281" t="s">
         <v>1275</v>
-      </c>
-      <c r="D281" t="s">
-        <v>1276</v>
       </c>
       <c r="E281" t="s">
         <v>90</v>
       </c>
       <c r="F281" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G281" t="s">
         <v>61</v>
@@ -39489,19 +39486,19 @@
         <v>109</v>
       </c>
       <c r="B282" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C282" t="s">
         <v>1277</v>
       </c>
-      <c r="C282" t="s">
+      <c r="D282" t="s">
         <v>1278</v>
-      </c>
-      <c r="D282" t="s">
-        <v>1279</v>
       </c>
       <c r="E282" t="s">
         <v>42</v>
       </c>
       <c r="F282" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G282" t="s">
         <v>44</v>
@@ -39614,19 +39611,19 @@
         <v>109</v>
       </c>
       <c r="B283" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C283" t="s">
         <v>1280</v>
       </c>
-      <c r="C283" t="s">
+      <c r="D283" t="s">
         <v>1281</v>
-      </c>
-      <c r="D283" t="s">
-        <v>1282</v>
       </c>
       <c r="E283" t="s">
         <v>42</v>
       </c>
       <c r="F283" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G283" t="s">
         <v>61</v>
@@ -39647,19 +39644,19 @@
         <v>48</v>
       </c>
       <c r="M283" t="s">
+        <v>1282</v>
+      </c>
+      <c r="N283" t="s">
+        <v>50</v>
+      </c>
+      <c r="O283" t="s">
+        <v>50</v>
+      </c>
+      <c r="P283" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q283" t="s">
         <v>1283</v>
-      </c>
-      <c r="N283" t="s">
-        <v>50</v>
-      </c>
-      <c r="O283" t="s">
-        <v>50</v>
-      </c>
-      <c r="P283" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q283" t="s">
-        <v>1284</v>
       </c>
       <c r="R283" s="1">
         <v>121351000</v>
@@ -39739,19 +39736,19 @@
         <v>109</v>
       </c>
       <c r="B284" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C284" t="s">
         <v>1285</v>
       </c>
-      <c r="C284" t="s">
+      <c r="D284" t="s">
         <v>1286</v>
-      </c>
-      <c r="D284" t="s">
-        <v>1287</v>
       </c>
       <c r="E284" t="s">
         <v>90</v>
       </c>
       <c r="F284" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G284" t="s">
         <v>61</v>
@@ -39864,19 +39861,19 @@
         <v>109</v>
       </c>
       <c r="B285" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C285" t="s">
         <v>1288</v>
       </c>
-      <c r="C285" t="s">
+      <c r="D285" t="s">
         <v>1289</v>
-      </c>
-      <c r="D285" t="s">
-        <v>1290</v>
       </c>
       <c r="E285" t="s">
         <v>42</v>
       </c>
       <c r="F285" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G285" t="s">
         <v>61</v>
@@ -39897,7 +39894,7 @@
         <v>48</v>
       </c>
       <c r="M285" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="N285" t="s">
         <v>50</v>
@@ -39989,19 +39986,19 @@
         <v>123</v>
       </c>
       <c r="B286" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C286" t="s">
         <v>1292</v>
       </c>
-      <c r="C286" t="s">
+      <c r="D286" t="s">
         <v>1293</v>
-      </c>
-      <c r="D286" t="s">
-        <v>1294</v>
       </c>
       <c r="E286" t="s">
         <v>42</v>
       </c>
       <c r="F286" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G286" t="s">
         <v>44</v>
@@ -40022,19 +40019,19 @@
         <v>68</v>
       </c>
       <c r="M286" t="s">
+        <v>1294</v>
+      </c>
+      <c r="N286" t="s">
+        <v>50</v>
+      </c>
+      <c r="O286" t="s">
+        <v>50</v>
+      </c>
+      <c r="P286" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q286" t="s">
         <v>1295</v>
-      </c>
-      <c r="N286" t="s">
-        <v>50</v>
-      </c>
-      <c r="O286" t="s">
-        <v>50</v>
-      </c>
-      <c r="P286" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q286" t="s">
-        <v>1296</v>
       </c>
       <c r="R286" s="1">
         <v>161165342.27000001</v>
@@ -40114,19 +40111,19 @@
         <v>525</v>
       </c>
       <c r="B287" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C287" t="s">
         <v>1297</v>
       </c>
-      <c r="C287" t="s">
+      <c r="D287" t="s">
         <v>1298</v>
-      </c>
-      <c r="D287" t="s">
-        <v>1299</v>
       </c>
       <c r="E287" t="s">
         <v>42</v>
       </c>
       <c r="F287" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G287" t="s">
         <v>44</v>
@@ -40147,19 +40144,19 @@
         <v>48</v>
       </c>
       <c r="M287" t="s">
+        <v>1299</v>
+      </c>
+      <c r="N287" t="s">
+        <v>50</v>
+      </c>
+      <c r="O287" t="s">
+        <v>50</v>
+      </c>
+      <c r="P287" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q287" t="s">
         <v>1300</v>
-      </c>
-      <c r="N287" t="s">
-        <v>50</v>
-      </c>
-      <c r="O287" t="s">
-        <v>50</v>
-      </c>
-      <c r="P287" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q287" t="s">
-        <v>1301</v>
       </c>
       <c r="R287" s="1">
         <v>2574207735.6199999</v>
@@ -40239,19 +40236,19 @@
         <v>525</v>
       </c>
       <c r="B288" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C288" t="s">
         <v>1302</v>
       </c>
-      <c r="C288" t="s">
+      <c r="D288" t="s">
         <v>1303</v>
-      </c>
-      <c r="D288" t="s">
-        <v>1304</v>
       </c>
       <c r="E288" t="s">
         <v>42</v>
       </c>
       <c r="F288" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G288" t="s">
         <v>44</v>
@@ -40272,19 +40269,19 @@
         <v>48</v>
       </c>
       <c r="M288" t="s">
+        <v>1304</v>
+      </c>
+      <c r="N288" t="s">
+        <v>50</v>
+      </c>
+      <c r="O288" t="s">
+        <v>50</v>
+      </c>
+      <c r="P288" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q288" t="s">
         <v>1305</v>
-      </c>
-      <c r="N288" t="s">
-        <v>50</v>
-      </c>
-      <c r="O288" t="s">
-        <v>50</v>
-      </c>
-      <c r="P288" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q288" t="s">
-        <v>1306</v>
       </c>
       <c r="R288" s="1">
         <v>3019972709.1999998</v>
@@ -40364,19 +40361,19 @@
         <v>525</v>
       </c>
       <c r="B289" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C289" t="s">
         <v>1307</v>
       </c>
-      <c r="C289" t="s">
+      <c r="D289" t="s">
         <v>1308</v>
-      </c>
-      <c r="D289" t="s">
-        <v>1309</v>
       </c>
       <c r="E289" t="s">
         <v>42</v>
       </c>
       <c r="F289" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G289" t="s">
         <v>44</v>
@@ -40397,19 +40394,19 @@
         <v>68</v>
       </c>
       <c r="M289" t="s">
+        <v>1309</v>
+      </c>
+      <c r="N289" t="s">
+        <v>50</v>
+      </c>
+      <c r="O289" t="s">
+        <v>50</v>
+      </c>
+      <c r="P289" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q289" t="s">
         <v>1310</v>
-      </c>
-      <c r="N289" t="s">
-        <v>50</v>
-      </c>
-      <c r="O289" t="s">
-        <v>50</v>
-      </c>
-      <c r="P289" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q289" t="s">
-        <v>1311</v>
       </c>
       <c r="R289" s="1">
         <v>154264536.59999999</v>
@@ -40489,19 +40486,19 @@
         <v>208</v>
       </c>
       <c r="B290" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C290" t="s">
         <v>1312</v>
       </c>
-      <c r="C290" t="s">
+      <c r="D290" t="s">
         <v>1313</v>
-      </c>
-      <c r="D290" t="s">
-        <v>1314</v>
       </c>
       <c r="E290" t="s">
         <v>42</v>
       </c>
       <c r="F290" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G290" t="s">
         <v>44</v>
@@ -40534,7 +40531,7 @@
         <v>50</v>
       </c>
       <c r="Q290" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="R290" s="1">
         <v>631607.64</v>
@@ -40614,19 +40611,19 @@
         <v>259</v>
       </c>
       <c r="B291" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C291" t="s">
         <v>1317</v>
       </c>
-      <c r="C291" t="s">
+      <c r="D291" t="s">
         <v>1318</v>
-      </c>
-      <c r="D291" t="s">
-        <v>1319</v>
       </c>
       <c r="E291" t="s">
         <v>42</v>
       </c>
       <c r="F291" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G291" t="s">
         <v>61</v>
@@ -40739,19 +40736,19 @@
         <v>99</v>
       </c>
       <c r="B292" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C292" t="s">
         <v>1320</v>
       </c>
-      <c r="C292" t="s">
+      <c r="D292" t="s">
         <v>1321</v>
-      </c>
-      <c r="D292" t="s">
-        <v>1322</v>
       </c>
       <c r="E292" t="s">
         <v>42</v>
       </c>
       <c r="F292" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G292" t="s">
         <v>61</v>
@@ -40784,7 +40781,7 @@
         <v>47</v>
       </c>
       <c r="Q292" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="R292" s="1">
         <v>8279173.5999999996</v>
@@ -40864,19 +40861,19 @@
         <v>99</v>
       </c>
       <c r="B293" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C293" t="s">
         <v>1324</v>
       </c>
-      <c r="C293" t="s">
+      <c r="D293" t="s">
         <v>1325</v>
-      </c>
-      <c r="D293" t="s">
-        <v>1326</v>
       </c>
       <c r="E293" t="s">
         <v>42</v>
       </c>
       <c r="F293" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G293" t="s">
         <v>61</v>
@@ -40909,7 +40906,7 @@
         <v>47</v>
       </c>
       <c r="Q293" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="R293" s="1">
         <v>133671.17000000001</v>
@@ -40989,19 +40986,19 @@
         <v>170</v>
       </c>
       <c r="B294" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C294" t="s">
         <v>1327</v>
       </c>
-      <c r="C294" t="s">
+      <c r="D294" t="s">
         <v>1328</v>
-      </c>
-      <c r="D294" t="s">
-        <v>1329</v>
       </c>
       <c r="E294" t="s">
         <v>42</v>
       </c>
       <c r="F294" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G294" t="s">
         <v>61</v>
@@ -41022,19 +41019,19 @@
         <v>48</v>
       </c>
       <c r="M294" t="s">
+        <v>1329</v>
+      </c>
+      <c r="N294" t="s">
+        <v>50</v>
+      </c>
+      <c r="O294" t="s">
+        <v>50</v>
+      </c>
+      <c r="P294" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q294" t="s">
         <v>1330</v>
-      </c>
-      <c r="N294" t="s">
-        <v>50</v>
-      </c>
-      <c r="O294" t="s">
-        <v>50</v>
-      </c>
-      <c r="P294" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q294" t="s">
-        <v>1331</v>
       </c>
       <c r="R294" s="1">
         <v>5721177.9699999997</v>
@@ -41114,19 +41111,19 @@
         <v>109</v>
       </c>
       <c r="B295" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C295" t="s">
         <v>1332</v>
       </c>
-      <c r="C295" t="s">
+      <c r="D295" t="s">
         <v>1333</v>
-      </c>
-      <c r="D295" t="s">
-        <v>1334</v>
       </c>
       <c r="E295" t="s">
         <v>42</v>
       </c>
       <c r="F295" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G295" t="s">
         <v>44</v>
@@ -41239,19 +41236,19 @@
         <v>118</v>
       </c>
       <c r="B296" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C296" t="s">
         <v>1335</v>
       </c>
-      <c r="C296" t="s">
+      <c r="D296" t="s">
         <v>1336</v>
-      </c>
-      <c r="D296" t="s">
-        <v>1337</v>
       </c>
       <c r="E296" t="s">
         <v>42</v>
       </c>
       <c r="F296" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G296" t="s">
         <v>61</v>
@@ -41272,19 +41269,19 @@
         <v>48</v>
       </c>
       <c r="M296" t="s">
+        <v>1337</v>
+      </c>
+      <c r="N296" t="s">
+        <v>50</v>
+      </c>
+      <c r="O296" t="s">
+        <v>50</v>
+      </c>
+      <c r="P296" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q296" t="s">
         <v>1338</v>
-      </c>
-      <c r="N296" t="s">
-        <v>50</v>
-      </c>
-      <c r="O296" t="s">
-        <v>50</v>
-      </c>
-      <c r="P296" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q296" t="s">
-        <v>1339</v>
       </c>
       <c r="R296" s="1">
         <v>5069130</v>
@@ -41364,19 +41361,19 @@
         <v>132</v>
       </c>
       <c r="B297" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C297" t="s">
         <v>1340</v>
       </c>
-      <c r="C297" t="s">
+      <c r="D297" t="s">
         <v>1341</v>
-      </c>
-      <c r="D297" t="s">
-        <v>1342</v>
       </c>
       <c r="E297" t="s">
         <v>90</v>
       </c>
       <c r="F297" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G297" t="s">
         <v>61</v>
@@ -41486,19 +41483,19 @@
         <v>132</v>
       </c>
       <c r="B298" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C298" t="s">
         <v>1343</v>
       </c>
-      <c r="C298" t="s">
+      <c r="D298" t="s">
         <v>1344</v>
-      </c>
-      <c r="D298" t="s">
-        <v>1345</v>
       </c>
       <c r="E298" t="s">
         <v>42</v>
       </c>
       <c r="F298" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G298" t="s">
         <v>61</v>
@@ -41608,19 +41605,19 @@
         <v>136</v>
       </c>
       <c r="B299" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C299" t="s">
         <v>1346</v>
       </c>
-      <c r="C299" t="s">
+      <c r="D299" t="s">
         <v>1347</v>
-      </c>
-      <c r="D299" t="s">
-        <v>1348</v>
       </c>
       <c r="E299" t="s">
         <v>42</v>
       </c>
       <c r="F299" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G299" t="s">
         <v>61</v>
@@ -41653,7 +41650,7 @@
         <v>47</v>
       </c>
       <c r="Q299" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="R299" s="1">
         <v>33670.410000000003</v>
@@ -41761,6 +41758,16 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="46b55141-4b2f-4258-a573-db1c39b0939f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100802D7DD22AF86D4185DB969840DAB2EC" ma:contentTypeVersion="16" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="800fb11532f41225bd9a68a9930bb3b6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="46b55141-4b2f-4258-a573-db1c39b0939f" xmlns:ns3="2f4a01b5-f148-4a33-9aef-843534c709be" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7581131fd7acacf8693bb33a4571527a" ns2:_="" ns3:_="">
     <xsd:import namespace="46b55141-4b2f-4258-a573-db1c39b0939f"/>
@@ -41997,16 +42004,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="46b55141-4b2f-4258-a573-db1c39b0939f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E47CDBB6-1A59-4E06-A6C6-0174EF6ACEBF}">
   <ds:schemaRefs>
@@ -42016,6 +42013,16 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F008C6A8-5A78-4279-A70D-563BD709BF28}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="46b55141-4b2f-4258-a573-db1c39b0939f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{745C6882-F0D0-45AF-91F9-6613DB64BF38}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42034,16 +42041,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F008C6A8-5A78-4279-A70D-563BD709BF28}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="46b55141-4b2f-4258-a573-db1c39b0939f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{b5661350-c2e4-43dc-bce8-f003ddf8a3c4}" enabled="0" method="" siteId="{b5661350-c2e4-43dc-bce8-f003ddf8a3c4}" removed="1"/>
